--- a/Catalogo_UY_Completo.xlsx
+++ b/Catalogo_UY_Completo.xlsx
@@ -3274,10 +3274,10 @@
     <t>Características y especificaciones Características y especificaciones Ideales para proteger paredes de: Choques. Marcas. Roturas producidas por las manijas de puertas y ventanas. Cuadros. Espejos. Cajones. Bordes de mesas. Puertas corredizas. Presentación: Redondas Simil Madera 4 unidades</t>
   </si>
   <si>
-    <t>SBD TR PR 25 B 1.JPG</t>
-  </si>
-  <si>
-    <t>SBD TR PR 50 B 1.JPG</t>
+    <t>SBD TR PR 25 B 1.jpg</t>
+  </si>
+  <si>
+    <t>SBD TR PR 50 B 1.jpg</t>
   </si>
   <si>
     <t>SBD TR 1 - 1151.jpg</t>
@@ -3298,10 +3298,10 @@
     <t>SBD TR 12 - 1152.jpg</t>
   </si>
   <si>
-    <t>SBD TR 25 T 1.JPG</t>
-  </si>
-  <si>
-    <t>COM SBD TR C 1.JPG</t>
+    <t>SBD TR 25 T 1.jpg</t>
+  </si>
+  <si>
+    <t>COM SBD TR C 1.jpg</t>
   </si>
   <si>
     <t>SBD 12 ST - 1142.jpg</t>
@@ -3313,7 +3313,7 @@
     <t>SBD 125 ST - 1144.jpg</t>
   </si>
   <si>
-    <t>SBD 25 BST 1.JPG</t>
+    <t>SBD 25 BST 1.jpg</t>
   </si>
   <si>
     <t>SBD 25 ST - 1145.jpg</t>
@@ -3325,16 +3325,16 @@
     <t>PBD 125 - 1044.jpg</t>
   </si>
   <si>
-    <t>PBD 125 M E 1.JPG</t>
-  </si>
-  <si>
-    <t>PBD 25 T M 1.JPG</t>
+    <t>PBD 125 M E 1.jpg</t>
+  </si>
+  <si>
+    <t>PBD 25 T M 1.jpg</t>
   </si>
   <si>
     <t>PBD 50 - 1048.jpg</t>
   </si>
   <si>
-    <t>SBD TR PR 100 E 1.JPG</t>
+    <t>SBD TR PR 100 E 1.jpg</t>
   </si>
   <si>
     <t>EX A - 2117.jpg</t>
@@ -3349,7 +3349,7 @@
     <t>EXB 80 - 2120.jpg</t>
   </si>
   <si>
-    <t>SPX SA NS 10 T E 1.JPG</t>
+    <t>SPX SA NS 10 T E 1.jpg</t>
   </si>
   <si>
     <t>SPX SA 25 A E - 10976.jpg</t>
@@ -3364,7 +3364,7 @@
     <t>MTJ 150 - 1035.jpg</t>
   </si>
   <si>
-    <t>ZAP 10 B 1.JPG</t>
+    <t>ZAP 10 B 1.jpg</t>
   </si>
   <si>
     <t>PTT 30 - 1079.jpg</t>
@@ -3376,7 +3376,7 @@
     <t>SPS P49 - 1182.jpg</t>
   </si>
   <si>
-    <t>DBL 30 B T 1.JPG</t>
+    <t>DBL 30 B T 1.jpg</t>
   </si>
   <si>
     <t>NSS 10 - 1037.jpg</t>
@@ -3409,7 +3409,7 @@
     <t>SLT V I - 1178.jpg</t>
   </si>
   <si>
-    <t>SLT V M I 1.JPG</t>
+    <t>SLT V M I 1.jpg</t>
   </si>
   <si>
     <t>SLT D 5 M I - 10961.jpg</t>
@@ -3460,13 +3460,13 @@
     <t>ZNO M I.jpg</t>
   </si>
   <si>
-    <t>ZNO D B 1.JPG</t>
+    <t>ZNO D B 1.jpg</t>
   </si>
   <si>
     <t>ZNO D G - 11010.jpg</t>
   </si>
   <si>
-    <t>ZNO D M 1.JPG</t>
+    <t>ZNO D M 1.jpg</t>
   </si>
   <si>
     <t>ZNO D N - 11014.jpg</t>
@@ -3484,10 +3484,10 @@
     <t>ZNO D B 120 - 11001.jpg</t>
   </si>
   <si>
-    <t>ZNO D G 120 1.JPG</t>
-  </si>
-  <si>
-    <t>ZNO D M 120 1.JPG</t>
+    <t>ZNO D G 120 1.jpg</t>
+  </si>
+  <si>
+    <t>ZNO D M 120 1.jpg</t>
   </si>
   <si>
     <t>CDB BS 20 - 120.jpg</t>
@@ -3556,7 +3556,7 @@
     <t>CDB AR 40X2 - 105.jpg</t>
   </si>
   <si>
-    <t>CDB AR 80 P 1.JPG</t>
+    <t>CDB AR 80 P 1.jpg</t>
   </si>
   <si>
     <t>CDB AS 40 - 111.jpg</t>
@@ -3622,22 +3622,22 @@
     <t>CDB C3 35 TSA C - 128.jpg</t>
   </si>
   <si>
-    <t>CAS BI M B 1.JPG</t>
-  </si>
-  <si>
-    <t>CAS BI L B 1.JPG</t>
-  </si>
-  <si>
-    <t>CAS BI L N 1.JPG</t>
-  </si>
-  <si>
-    <t>CAS BI L R 1.JPG</t>
-  </si>
-  <si>
-    <t>CAS BI M N 1.JPG</t>
-  </si>
-  <si>
-    <t>CAS BI M R 1.JPG</t>
+    <t>CAS BI M B 1.jpg</t>
+  </si>
+  <si>
+    <t>CAS BI L B 1.jpg</t>
+  </si>
+  <si>
+    <t>CAS BI L N 1.jpg</t>
+  </si>
+  <si>
+    <t>CAS BI L R 1.jpg</t>
+  </si>
+  <si>
+    <t>CAS BI M N 1.jpg</t>
+  </si>
+  <si>
+    <t>CAS BI M R 1.jpg</t>
   </si>
   <si>
     <t>CAD 38 1.5 - 1318.jpg</t>
@@ -3646,7 +3646,7 @@
     <t>CAD 14 1 - 91.jpg</t>
   </si>
   <si>
-    <t>CAD 1/CAD 1/4 14 1 1.JPG</t>
+    <t>CAD 1/CAD 1/4 14 1 1.jpg</t>
   </si>
   <si>
     <t>CAD 38 1 - 93.jpg</t>
@@ -3673,25 +3673,25 @@
     <t>CDB TD 5.5 F - 1383.jpg</t>
   </si>
   <si>
-    <t>SGC CBO 6 E-L.5 1.JPG</t>
-  </si>
-  <si>
-    <t>SGC H 12-L.5 1.JPG</t>
-  </si>
-  <si>
-    <t>SGC H 6 L.5G01 1.JPG</t>
-  </si>
-  <si>
-    <t>SGC E 6 L.5K01 1.JPG</t>
-  </si>
-  <si>
-    <t>SGC CBO 6 E E 1.JPG</t>
-  </si>
-  <si>
-    <t>SGC E 12 1.JPG</t>
-  </si>
-  <si>
-    <t>RPM 250 1.JPG</t>
+    <t>SGC CBO 6 E-L.5 1.jpg</t>
+  </si>
+  <si>
+    <t>SGC H 12-L.5 1.jpg</t>
+  </si>
+  <si>
+    <t>SGC H 6 L.5G01 1.jpg</t>
+  </si>
+  <si>
+    <t>SGC E 6 L.5K01 1.jpg</t>
+  </si>
+  <si>
+    <t>SGC CBO 6 E E 1.jpg</t>
+  </si>
+  <si>
+    <t>SGC E 12 1.jpg</t>
+  </si>
+  <si>
+    <t>RPM 250 1.jpg</t>
   </si>
   <si>
     <t>PRT L2 FP - 1072.jpg</t>
@@ -3754,28 +3754,28 @@
     <t>SCR P 180 40 - 1159.jpg</t>
   </si>
   <si>
-    <t>SCR P 180 60 1.JPG</t>
+    <t>SCR P 180 60 1.jpg</t>
   </si>
   <si>
     <t>CAB - 1303.jpg</t>
   </si>
   <si>
-    <t>CAB 2 1.JPG</t>
+    <t>CAB 2 1.jpg</t>
   </si>
   <si>
     <t>CAB PRO PR - 1312.jpg</t>
   </si>
   <si>
-    <t>CAB PRO PR GM 1.JPG</t>
-  </si>
-  <si>
-    <t>CAB PRO PR GP 1.JPG</t>
-  </si>
-  <si>
-    <t>CAB PRO 1.JPG</t>
-  </si>
-  <si>
-    <t>CAB INT 2 1.JPG</t>
+    <t>CAB PRO PR GM 1.jpg</t>
+  </si>
+  <si>
+    <t>CAB PRO PR GP 1.jpg</t>
+  </si>
+  <si>
+    <t>CAB PRO 1.jpg</t>
+  </si>
+  <si>
+    <t>CAB INT 2 1.jpg</t>
   </si>
   <si>
     <t>CAB CP 15 - 1304.jpg</t>
@@ -3835,7 +3835,7 @@
     <t>DES 8PHA 1X100 - 2003.jpg</t>
   </si>
   <si>
-    <t>DES 8 PHA 0X75 1.JPG</t>
+    <t>DES 8 PHA 0X75 1.jpg</t>
   </si>
   <si>
     <t>DES 8PHA 0X75 - 778.jpg</t>
@@ -3853,10 +3853,10 @@
     <t>DES 8RA 5.5X125 - 2022.jpg</t>
   </si>
   <si>
-    <t>DES 7RA 4X150 1.JPG</t>
-  </si>
-  <si>
-    <t>DES 7RA 4X75 1.JPG</t>
+    <t>DES 7RA 4X150 1.jpg</t>
+  </si>
+  <si>
+    <t>DES 7RA 4X75 1.jpg</t>
   </si>
   <si>
     <t>DES 7PH 0X50 - 1971.jpg</t>
@@ -3919,22 +3919,22 @@
     <t>DES 7PL 8X150 - 766.jpg</t>
   </si>
   <si>
-    <t>DES 7RT 4X150 1.JPG</t>
-  </si>
-  <si>
-    <t>DES 7RT 4X75 1.JPG</t>
-  </si>
-  <si>
-    <t>DES 7RT 5X150 1.JPG</t>
-  </si>
-  <si>
-    <t>DES 8 ST 6 1.JPG</t>
-  </si>
-  <si>
-    <t>DES 8A ST 6 1.JPG</t>
-  </si>
-  <si>
-    <t>LLV 7C KIT 5 R 1.JPG</t>
+    <t>DES 7RT 4X150 1.jpg</t>
+  </si>
+  <si>
+    <t>DES 7RT 4X75 1.jpg</t>
+  </si>
+  <si>
+    <t>DES 7RT 5X150 1.jpg</t>
+  </si>
+  <si>
+    <t>DES 8 ST 6 1.jpg</t>
+  </si>
+  <si>
+    <t>DES 8A ST 6 1.jpg</t>
+  </si>
+  <si>
+    <t>LLV 7C KIT 5 R 1.jpg</t>
   </si>
   <si>
     <t>CH ALM 9 - 1390.jpg</t>
@@ -3988,7 +3988,7 @@
     <t>PZA S6 AJ8 - 1109.jpg</t>
   </si>
   <si>
-    <t>PZA FZA 6.5 1.JPG</t>
+    <t>PZA FZA 6.5 1.jpg</t>
   </si>
   <si>
     <t>PZA FZ10 - 1094.jpg</t>
@@ -4054,10 +4054,10 @@
     <t>PZA P8 PS6 - 1103.jpg</t>
   </si>
   <si>
-    <t>PZA S6 SET 3 1.JPG</t>
-  </si>
-  <si>
-    <t>PZA S8 SET 3 1.JPG</t>
+    <t>PZA S6 SET 3 1.jpg</t>
+  </si>
+  <si>
+    <t>PZA S8 SET 3 1.jpg</t>
   </si>
   <si>
     <t>PZA S6 TN A12 - 1129.jpg</t>
@@ -4090,25 +4090,25 @@
     <t>PZA AV R - 1086.jpg</t>
   </si>
   <si>
-    <t>CTA MCA 5C 7,5 1.JPG</t>
-  </si>
-  <si>
-    <t>CTA MCA 5B 5 1.JPG</t>
-  </si>
-  <si>
-    <t>CTA MCA 5B 3 1.JPG</t>
-  </si>
-  <si>
-    <t>CTA MCA 5B 7,5 1.JPG</t>
-  </si>
-  <si>
-    <t>CTA MCA 5C 3 1.JPG</t>
-  </si>
-  <si>
-    <t>CTA MCA 5C 5 1.JPG</t>
-  </si>
-  <si>
-    <t>CTA MCA7F 8 1.JPG</t>
+    <t>CTA MCA 5C 7,5 1.jpg</t>
+  </si>
+  <si>
+    <t>CTA MCA 5B 5 1.jpg</t>
+  </si>
+  <si>
+    <t>CTA MCA 5B 3 1.jpg</t>
+  </si>
+  <si>
+    <t>CTA MCA 5B 7,5 1.jpg</t>
+  </si>
+  <si>
+    <t>CTA MCA 5C 3 1.jpg</t>
+  </si>
+  <si>
+    <t>CTA MCA 5C 5 1.jpg</t>
+  </si>
+  <si>
+    <t>CTA MCA7F 8 1.jpg</t>
   </si>
   <si>
     <t>MBN VEN 1 B - 1013.jpg</t>
@@ -4138,7 +4138,7 @@
     <t>JD S6 PZA BY - 2160.jpg</t>
   </si>
   <si>
-    <t>JD S8 PZA BY 1.JPG</t>
+    <t>JD S8 PZA BY 1.jpg</t>
   </si>
   <si>
     <t>JD S8 TIJ PD A - 10739.jpg</t>
@@ -4201,7 +4201,7 @@
     <t>C PX 2100 - 1301.jpg</t>
   </si>
   <si>
-    <t>C PHX 100 1.JPG</t>
+    <t>C PHX 100 1.jpg</t>
   </si>
   <si>
     <t>C PX 300 - 1302.jpg</t>
@@ -4210,19 +4210,19 @@
     <t>C PHX 200 R - 1300.jpg</t>
   </si>
   <si>
-    <t>PHB BO C BT 36 1.JPG</t>
-  </si>
-  <si>
-    <t>PHB BO C 42 1.JPG</t>
-  </si>
-  <si>
-    <t>PHB BO 32 1.JPG</t>
-  </si>
-  <si>
-    <t>PHB C 2CA 1.JPG</t>
-  </si>
-  <si>
-    <t>PHB MO 35 1.JPG</t>
+    <t>PHB BO C BT 36 1.jpg</t>
+  </si>
+  <si>
+    <t>PHB BO C 42 1.jpg</t>
+  </si>
+  <si>
+    <t>PHB BO 32 1.jpg</t>
+  </si>
+  <si>
+    <t>PHB C 2CA 1.jpg</t>
+  </si>
+  <si>
+    <t>PHB MO 35 1.jpg</t>
   </si>
   <si>
     <t>GMX ACR 110 B - 2143.jpg</t>
@@ -4252,10 +4252,10 @@
     <t>EPP PU 500 P - 2090.jpg</t>
   </si>
   <si>
-    <t>EPP PU 750 E 1.JPG</t>
-  </si>
-  <si>
-    <t>EPP PU 750 P 1.JPG</t>
+    <t>EPP PU 750 E 1.jpg</t>
+  </si>
+  <si>
+    <t>EPP PU 750 P 1.jpg</t>
   </si>
   <si>
     <t>PST GR - 1075.jpg</t>
@@ -4264,10 +4264,10 @@
     <t>PST PL 800 - 1078.jpg</t>
   </si>
   <si>
-    <t>GAS 125 E 1.JPG</t>
-  </si>
-  <si>
-    <t>GAS 125 1.JPG</t>
+    <t>GAS 125 E 1.jpg</t>
+  </si>
+  <si>
+    <t>GAS 125 1.jpg</t>
   </si>
   <si>
     <t>GAS 25 - 2122.jpg</t>
@@ -4282,7 +4282,7 @@
     <t>PBD 400 - 1046.jpg</t>
   </si>
   <si>
-    <t>PBD 25 T 1.JPG</t>
+    <t>PBD 25 T 1.jpg</t>
   </si>
   <si>
     <t>SMZ 50 A - 1181.jpg</t>
@@ -4291,7 +4291,7 @@
     <t>SMZ 300 A - 1180.jpg</t>
   </si>
   <si>
-    <t>PBD P 25 T 1.JPG</t>
+    <t>PBD P 25 T 1.jpg</t>
   </si>
   <si>
     <t>PBD P 50 - 1052.jpg</t>
@@ -4306,10 +4306,10 @@
     <t>GFX C 280 T - 2129.jpg</t>
   </si>
   <si>
-    <t>GFX AT S5 280 R 1.JPG</t>
-  </si>
-  <si>
-    <t>GFX A S5 280 T 1.JPG</t>
+    <t>GFX AT S5 280 R 1.jpg</t>
+  </si>
+  <si>
+    <t>GFX A S5 280 T 1.jpg</t>
   </si>
   <si>
     <t>GFX J 110 R - 2130.jpg</t>
@@ -4321,7 +4321,7 @@
     <t>GFX C 110 T - 2128.jpg</t>
   </si>
   <si>
-    <t>GFX N S5 280 T 1.JPG</t>
+    <t>GFX N S5 280 T 1.jpg</t>
   </si>
   <si>
     <t>GFX U 280 B - 2136.jpg</t>
@@ -4348,19 +4348,19 @@
     <t>GFX U 60 T - 2141.jpg</t>
   </si>
   <si>
-    <t>RTR ESP 1.JPG</t>
+    <t>RTR ESP 1.jpg</t>
   </si>
   <si>
     <t>KIT PRB - 2175.jpg</t>
   </si>
   <si>
-    <t>KIT R OP 1.JPG</t>
+    <t>KIT R OP 1.jpg</t>
   </si>
   <si>
     <t>AFX VA 2 - 1240.jpg</t>
   </si>
   <si>
-    <t>AFX CA 25X5 N 1.JPG</t>
+    <t>AFX CA 25X5 N 1.jpg</t>
   </si>
   <si>
     <t>AFX W 16 - 1242.jpg</t>
@@ -4372,58 +4372,58 @@
     <t>AFX S E - 1238.jpg</t>
   </si>
   <si>
-    <t>AFX P66 BO 1.JPG</t>
-  </si>
-  <si>
-    <t>AFX P54 BO 1.JPG</t>
+    <t>AFX P66 BO 1.jpg</t>
+  </si>
+  <si>
+    <t>AFX P54 BO 1.jpg</t>
   </si>
   <si>
     <t>AFX P54 TO - 1.jpg</t>
   </si>
   <si>
-    <t>AFX P35 BO 1.JPG</t>
+    <t>AFX P35 BO 1.jpg</t>
   </si>
   <si>
     <t>AFX P35 TO.jpg</t>
   </si>
   <si>
-    <t>AFX P49 AR 1.JPG</t>
+    <t>AFX P49 AR 1.jpg</t>
   </si>
   <si>
     <t>AFX P18 AR - 2451.jpg</t>
   </si>
   <si>
-    <t>AFX PEA 4 T 1.JPG</t>
+    <t>AFX PEA 4 T 1.jpg</t>
   </si>
   <si>
     <t>AFX RUE 4 AI - 1237.jpg</t>
   </si>
   <si>
-    <t>AFX PC 1 20 1.JPG</t>
-  </si>
-  <si>
-    <t>AFX MP 1X2,2 N 1.JPG</t>
-  </si>
-  <si>
-    <t>AFX MV 1,3X1,6 N 1.JPG</t>
-  </si>
-  <si>
-    <t>AFX MV 2X2 N 1.JPG</t>
-  </si>
-  <si>
-    <t>AFX MV 1X1,2 N 1.JPG</t>
-  </si>
-  <si>
-    <t>AFX P R33 B 1.JPG</t>
-  </si>
-  <si>
-    <t>AFX P R80 BO 1.JPG</t>
-  </si>
-  <si>
-    <t>AFX P R80 TO 1.JPG</t>
-  </si>
-  <si>
-    <t>AFX ZP 7X5 B 1.JPG</t>
+    <t>AFX PC 1 20 1.jpg</t>
+  </si>
+  <si>
+    <t>AFX MP 1X2,2 N 1.jpg</t>
+  </si>
+  <si>
+    <t>AFX MV 1,3X1,6 N 1.jpg</t>
+  </si>
+  <si>
+    <t>AFX MV 2X2 N 1.jpg</t>
+  </si>
+  <si>
+    <t>AFX MV 1X1,2 N 1.jpg</t>
+  </si>
+  <si>
+    <t>AFX P R33 B 1.jpg</t>
+  </si>
+  <si>
+    <t>AFX P R80 BO 1.jpg</t>
+  </si>
+  <si>
+    <t>AFX P R80 TO 1.jpg</t>
+  </si>
+  <si>
+    <t>AFX ZP 7X5 B 1.jpg</t>
   </si>
   <si>
     <t>TPC F 20 M - 1195.jpg</t>

--- a/Catalogo_UY_Completo.xlsx
+++ b/Catalogo_UY_Completo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3561" uniqueCount="1483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3561" uniqueCount="1481">
   <si>
     <t>Producto_id</t>
   </si>
@@ -3304,13 +3304,13 @@
     <t>COM SBD TR C 1.jpg</t>
   </si>
   <si>
-    <t>SBD 12 ST - 1142.jpg</t>
-  </si>
-  <si>
-    <t>SBD 14 ST - 1143.jpg</t>
-  </si>
-  <si>
-    <t>SBD 125 ST - 1144.jpg</t>
+    <t>SBD 12 ST - 1142.jpeg</t>
+  </si>
+  <si>
+    <t>SBD 14 ST - 1143.jpeg</t>
+  </si>
+  <si>
+    <t>SBD 125 ST - 1144.jpeg</t>
   </si>
   <si>
     <t>SBD 25 BST 1.jpg</t>
@@ -3319,31 +3319,31 @@
     <t>SBD 25 ST - 1145.jpg</t>
   </si>
   <si>
-    <t>SBD 50 ST - 1147.jpg</t>
-  </si>
-  <si>
-    <t>PBD 125 - 1044.jpg</t>
+    <t>SBD 50 ST - 1147.jpeg</t>
+  </si>
+  <si>
+    <t>PBD 125 1.jpg</t>
   </si>
   <si>
     <t>PBD 125 M E 1.jpg</t>
   </si>
   <si>
-    <t>PBD 25 T M 1.jpg</t>
-  </si>
-  <si>
-    <t>PBD 50 - 1048.jpg</t>
+    <t>PBD 25 T 1.jpg</t>
+  </si>
+  <si>
+    <t>PBD 50 1.jpg</t>
   </si>
   <si>
     <t>SBD TR PR 100 E 1.jpg</t>
   </si>
   <si>
-    <t>EX A - 2117.jpg</t>
+    <t>EX A - 2117.jpeg</t>
   </si>
   <si>
     <t>EX A 105 - 2118.jpg</t>
   </si>
   <si>
-    <t>EXB - 2119.jpg</t>
+    <t>EXB - 2119.jpeg</t>
   </si>
   <si>
     <t>EXB 80 - 2120.jpg</t>
@@ -3352,10 +3352,10 @@
     <t>SPX SA NS 10 T E 1.jpg</t>
   </si>
   <si>
-    <t>SPX SA 25 A E - 10976.jpg</t>
-  </si>
-  <si>
-    <t>SPX SA 16 T E - 1183.jpg</t>
+    <t>SPX SA 25 A E - 10976.jpeg</t>
+  </si>
+  <si>
+    <t>SPX SA 16 T E - 1183.jpeg</t>
   </si>
   <si>
     <t>MTJ 400 - 1036.jpg</t>
@@ -3367,13 +3367,13 @@
     <t>ZAP 10 B 1.jpg</t>
   </si>
   <si>
-    <t>PTT 30 - 1079.jpg</t>
-  </si>
-  <si>
-    <t>PVN 25 B - 1080.jpg</t>
-  </si>
-  <si>
-    <t>SPS P49 - 1182.jpg</t>
+    <t>PTT 30 1.jpg</t>
+  </si>
+  <si>
+    <t>PVN 25 B - 1080.jpeg</t>
+  </si>
+  <si>
+    <t>SPS P49 - 1182.jpeg</t>
   </si>
   <si>
     <t>DBL 30 B T 1.jpg</t>
@@ -3382,10 +3382,10 @@
     <t>NSS 10 - 1037.jpg</t>
   </si>
   <si>
-    <t>ARN FL 1X3 B - 1244.jpg</t>
-  </si>
-  <si>
-    <t>ARN FL 2 B - 1245.jpg</t>
+    <t>ARN FL 1X3 B - 1244.jpeg</t>
+  </si>
+  <si>
+    <t>ARN FL 2 B - 1245.jpeg</t>
   </si>
   <si>
     <t>ARN FL 2 T.jpg</t>
@@ -3403,55 +3403,55 @@
     <t>ESL 30 - 2094.jpg</t>
   </si>
   <si>
-    <t>CIA A-40 20 - 1396.jpg</t>
-  </si>
-  <si>
-    <t>SLT V I - 1178.jpg</t>
+    <t>CIA A-40 20 1.jpg</t>
+  </si>
+  <si>
+    <t>SLT V I - 1178.jpeg</t>
   </si>
   <si>
     <t>SLT V M I 1.jpg</t>
   </si>
   <si>
-    <t>SLT D 5 M I - 10961.jpg</t>
-  </si>
-  <si>
-    <t>SLT P 5 M I - 1177.jpg</t>
-  </si>
-  <si>
-    <t>SLT E 5 B I - 10963.jpg</t>
-  </si>
-  <si>
-    <t>SLT D 5 B I - 10960.jpg</t>
-  </si>
-  <si>
-    <t>SLT P 5 B I - 10968.jpg</t>
-  </si>
-  <si>
-    <t>SLT E 5 M I - 1172.jpg</t>
-  </si>
-  <si>
-    <t>SLT D - 1167.jpg</t>
-  </si>
-  <si>
-    <t>SLT EA - 1173.jpg</t>
-  </si>
-  <si>
-    <t>SLT N - 1175.jpg</t>
-  </si>
-  <si>
-    <t>SLT D M - 1170.jpg</t>
-  </si>
-  <si>
-    <t>SLT EA M - 1174.jpg</t>
-  </si>
-  <si>
-    <t>ZNO B - 10997.jpg</t>
-  </si>
-  <si>
-    <t>ZNO - 1204.jpg</t>
-  </si>
-  <si>
-    <t>ZNO SM - 1224.jpg</t>
+    <t>SLT D 5 M I - 10961.jpeg</t>
+  </si>
+  <si>
+    <t>SLT P 5 M I - 1177.jpeg</t>
+  </si>
+  <si>
+    <t>SLT E 5 B I - 10963.jpeg</t>
+  </si>
+  <si>
+    <t>SLT D 5 B I - 10960.jpeg</t>
+  </si>
+  <si>
+    <t>SLT P 5 B I - 10968.jpeg</t>
+  </si>
+  <si>
+    <t>SLT E 5 M I - 1172.jpeg</t>
+  </si>
+  <si>
+    <t>SLT D - 1167.jpeg</t>
+  </si>
+  <si>
+    <t>SLT EA - 1173.jpeg</t>
+  </si>
+  <si>
+    <t>SLT N - 1175.jpeg</t>
+  </si>
+  <si>
+    <t>SLT D M - 1170.jpeg</t>
+  </si>
+  <si>
+    <t>SLT EA M - 1174.jpeg</t>
+  </si>
+  <si>
+    <t>ZNO B - 10997.jpeg</t>
+  </si>
+  <si>
+    <t>ZNO - 1204.jpeg</t>
+  </si>
+  <si>
+    <t>ZNO SM - 1224.jpeg</t>
   </si>
   <si>
     <t>ZNO B I.jpg</t>
@@ -3463,22 +3463,22 @@
     <t>ZNO D B 1.jpg</t>
   </si>
   <si>
-    <t>ZNO D G - 11010.jpg</t>
+    <t>ZNO D G - 11010.jpeg</t>
   </si>
   <si>
     <t>ZNO D M 1.jpg</t>
   </si>
   <si>
-    <t>ZNO D N - 11014.jpg</t>
-  </si>
-  <si>
-    <t>ZNO D EA B - 11002.jpg</t>
-  </si>
-  <si>
-    <t>ZNO D EA G - 11004.jpg</t>
-  </si>
-  <si>
-    <t>ZNO D EA M - 11006.jpg</t>
+    <t>ZNO D N - 11014.jpeg</t>
+  </si>
+  <si>
+    <t>ZNO D EA B - 11002.jpeg</t>
+  </si>
+  <si>
+    <t>ZNO D EA G - 11004.jpeg</t>
+  </si>
+  <si>
+    <t>ZNO D EA M - 11006.jpeg</t>
   </si>
   <si>
     <t>ZNO D B 120 - 11001.jpg</t>
@@ -3505,55 +3505,55 @@
     <t>CDB H 60 - 146.jpg</t>
   </si>
   <si>
-    <t>CDB H 30 D - 1362.jpg</t>
-  </si>
-  <si>
-    <t>CDB H 30 D L - 1363.jpg</t>
-  </si>
-  <si>
-    <t>CDB H 40 D - 141.jpg</t>
-  </si>
-  <si>
-    <t>CDB H 40 D L - 1366.jpg</t>
-  </si>
-  <si>
-    <t>CDB H 50 D - 1368.jpg</t>
-  </si>
-  <si>
-    <t>CDB H 50 D L - 1369.jpg</t>
-  </si>
-  <si>
-    <t>CDB H 60 D - 1371.jpg</t>
-  </si>
-  <si>
-    <t>CDB MS 72 B - 1379.jpg</t>
+    <t>CDB H 30 D - 1362.jpeg</t>
+  </si>
+  <si>
+    <t>CDB H 30 D L - 1363.jpeg</t>
+  </si>
+  <si>
+    <t>CDB H 40 D - 141.jpeg</t>
+  </si>
+  <si>
+    <t>CDB H 40 D L - 1366.jpeg</t>
+  </si>
+  <si>
+    <t>CDB H 50 D - 1368.jpeg</t>
+  </si>
+  <si>
+    <t>CDB H 50 D L - 1369.jpeg</t>
+  </si>
+  <si>
+    <t>CDB H 60 D - 1371.jpeg</t>
+  </si>
+  <si>
+    <t>CDB MS 72 B - 1379.jpeg</t>
   </si>
   <si>
     <t>CDB AR 30 - 101.jpg</t>
   </si>
   <si>
-    <t>CDB AR 30 L - 102.jpg</t>
+    <t>CDB AR 30 L - 102.jpeg</t>
   </si>
   <si>
     <t>CDB AR 40 - 103.jpg</t>
   </si>
   <si>
-    <t>CDB AR 40 L - 104.jpg</t>
-  </si>
-  <si>
-    <t>CDB AR 40X4 - 106.jpg</t>
+    <t>CDB AR 40 L - 104.jpeg</t>
+  </si>
+  <si>
+    <t>CDB AR 40X4 - 106.jpeg</t>
   </si>
   <si>
     <t>CDB AR 50 - 107.jpg</t>
   </si>
   <si>
-    <t>CDB AR 50 L - 108.jpg</t>
+    <t>CDB AR 50 L - 108.jpeg</t>
   </si>
   <si>
     <t>CDB AR 60 - 109.jpg</t>
   </si>
   <si>
-    <t>CDB AR 40X2 - 105.jpg</t>
+    <t>CDB AR 40X2 - 105.jpeg</t>
   </si>
   <si>
     <t>CDB AR 80 P 1.jpg</t>
@@ -3565,7 +3565,7 @@
     <t>CDB AS 50 - 112.jpg</t>
   </si>
   <si>
-    <t>CDB WR 40 L - 1387.jpg</t>
+    <t>CDB WR 40 L - 1387.jpeg</t>
   </si>
   <si>
     <t>CDB WR 40 - 1386.jpg</t>
@@ -3574,10 +3574,10 @@
     <t>CDB WR 50 - 1388.jpg</t>
   </si>
   <si>
-    <t>CDB WR 50 L - 1389.jpg</t>
-  </si>
-  <si>
-    <t>CDB H 60 D L - 1372.jpg</t>
+    <t>CDB WR 50 L - 1389.jpeg</t>
+  </si>
+  <si>
+    <t>CDB H 60 D L - 1372.jpeg</t>
   </si>
   <si>
     <t>CDB H 30 - 1361.jpg</t>
@@ -3598,28 +3598,28 @@
     <t>CDB BR 50 - 118.jpg</t>
   </si>
   <si>
-    <t>CDB C4 PP - 132.jpg</t>
-  </si>
-  <si>
-    <t>CDB C5 65 CA - 133.jpg</t>
-  </si>
-  <si>
-    <t>CDB C5 65 CR - 134.jpg</t>
-  </si>
-  <si>
-    <t>CDB C3 20 AR - 123.jpg</t>
-  </si>
-  <si>
-    <t>CDB C3 30 AR - 125.jpg</t>
-  </si>
-  <si>
-    <t>CDB C4 40 AR - 129.jpg</t>
-  </si>
-  <si>
-    <t>CDB C3 35 TSA A - 127.jpg</t>
-  </si>
-  <si>
-    <t>CDB C3 35 TSA C - 128.jpg</t>
+    <t>CDB C4 PP - 132.jpeg</t>
+  </si>
+  <si>
+    <t>CDB C5 65 CA - 133.jpeg</t>
+  </si>
+  <si>
+    <t>CDB C5 65 CR - 134.jpeg</t>
+  </si>
+  <si>
+    <t>CDB C3 20 AR - 123.jpeg</t>
+  </si>
+  <si>
+    <t>CDB C3 30 AR - 125.jpeg</t>
+  </si>
+  <si>
+    <t>CDB C4 40 AR - 129.jpeg</t>
+  </si>
+  <si>
+    <t>CDB C3 35 TSA A - 127.jpeg</t>
+  </si>
+  <si>
+    <t>CDB C3 35 TSA C - 128.jpeg</t>
   </si>
   <si>
     <t>CAS BI M B 1.jpg</t>
@@ -3640,7 +3640,7 @@
     <t>CAS BI M R 1.jpg</t>
   </si>
   <si>
-    <t>CAD 38 1.5 - 1318.jpg</t>
+    <t>CAD 38 1.5 - 1318.jpeg</t>
   </si>
   <si>
     <t>CAD 14 1 - 91.jpg</t>
@@ -3652,25 +3652,25 @@
     <t>CAD 38 1 - 93.jpg</t>
   </si>
   <si>
-    <t>CDB CAD 10 1 C - 136.jpg</t>
+    <t>CDB CAD 10 1 C - 136.jpeg</t>
   </si>
   <si>
     <t>CDB LIN 180 - 1373.jpg</t>
   </si>
   <si>
-    <t>CDB LIN A120 LV - 1374.jpg</t>
-  </si>
-  <si>
-    <t>CDB LIN B CMB - 1375.jpg</t>
-  </si>
-  <si>
-    <t>CDB LIN B LV - 153.jpg</t>
-  </si>
-  <si>
-    <t>CDB T DISCO - 1381.jpg</t>
-  </si>
-  <si>
-    <t>CDB TD 5.5 F - 1383.jpg</t>
+    <t>CDB LIN A120 LV - 1374.jpeg</t>
+  </si>
+  <si>
+    <t>CDB LIN B CMB - 1375.jpeg</t>
+  </si>
+  <si>
+    <t>CDB LIN B LV - 153.jpeg</t>
+  </si>
+  <si>
+    <t>CDB T DISCO - 1381.jpeg</t>
+  </si>
+  <si>
+    <t>CDB TD 5.5 F - 1383.jpeg</t>
   </si>
   <si>
     <t>SGC CBO 6 E-L.5 1.jpg</t>
@@ -3685,7 +3685,7 @@
     <t>SGC E 6 L.5K01 1.jpg</t>
   </si>
   <si>
-    <t>SGC CBO 6 E E 1.jpg</t>
+    <t>SGC CBO 6 E 1.jpg</t>
   </si>
   <si>
     <t>SGC E 12 1.jpg</t>
@@ -3694,52 +3694,52 @@
     <t>RPM 250 1.jpg</t>
   </si>
   <si>
-    <t>PRT L2 FP - 1072.jpg</t>
-  </si>
-  <si>
-    <t>PRT R2 FP - 1073.jpg</t>
-  </si>
-  <si>
-    <t>DSA 4CP 115 1,6 - 2041.jpg</t>
+    <t>PRT L2 FP - 1072.jpeg</t>
+  </si>
+  <si>
+    <t>PRT R2 FP - 1073.jpeg</t>
+  </si>
+  <si>
+    <t>DSA 4CP 115 1,6 - 2041.jpeg</t>
   </si>
   <si>
     <t>DSA 4CP 115 1 - 816.jpg</t>
   </si>
   <si>
-    <t>DSA 4CP 180 1,6 - 2042.jpg</t>
-  </si>
-  <si>
-    <t>DSD S400 115 C - 2051.jpg</t>
-  </si>
-  <si>
-    <t>DSD S400 115 S - 828.jpg</t>
-  </si>
-  <si>
-    <t>DSD S400 180 S - 2056.jpg</t>
-  </si>
-  <si>
-    <t>DSD S400 230 S - 1.jpg</t>
-  </si>
-  <si>
-    <t>DSD S400 115 T - 2053.jpg</t>
-  </si>
-  <si>
-    <t>DSD S400 115 TF - 2054.jpg</t>
-  </si>
-  <si>
-    <t>DSD S80 115 C - 2067.jpg</t>
-  </si>
-  <si>
-    <t>DSD S80 180 C - 2070.jpg</t>
-  </si>
-  <si>
-    <t>DSD S80 230 S - 1.jpg</t>
-  </si>
-  <si>
-    <t>DSD S80 115 S - 2068.jpg</t>
-  </si>
-  <si>
-    <t>DSD S80 180 S - 2071.jpg</t>
+    <t>DSA 4CP 180 1,6 - 2042.jpeg</t>
+  </si>
+  <si>
+    <t>DSD S400 115 C - 2051.jpeg</t>
+  </si>
+  <si>
+    <t>DSD S400 115 S - 828.jpeg</t>
+  </si>
+  <si>
+    <t>DSD S400 180 S - 2056.jpeg</t>
+  </si>
+  <si>
+    <t>DSD S400 230 S - 1.jpeg</t>
+  </si>
+  <si>
+    <t>DSD S400 115 T - 2053.jpeg</t>
+  </si>
+  <si>
+    <t>DSD S400 115 TF - 2054.jpeg</t>
+  </si>
+  <si>
+    <t>DSD S80 115 C - 2067.jpeg</t>
+  </si>
+  <si>
+    <t>DSD S80 180 C - 2070.jpeg</t>
+  </si>
+  <si>
+    <t>DSD S80 230 S - 1.jpeg</t>
+  </si>
+  <si>
+    <t>DSD S80 115 S - 2068.jpeg</t>
+  </si>
+  <si>
+    <t>DSD S80 180 S - 2071.jpeg</t>
   </si>
   <si>
     <t>DSD S80 180 T - 1.jpg</t>
@@ -3757,13 +3757,13 @@
     <t>SCR P 180 60 1.jpg</t>
   </si>
   <si>
-    <t>CAB - 1303.jpg</t>
-  </si>
-  <si>
-    <t>CAB 2 1.jpg</t>
-  </si>
-  <si>
-    <t>CAB PRO PR - 1312.jpg</t>
+    <t>CAB - 1303.jpeg</t>
+  </si>
+  <si>
+    <t>CAB 2 1.JPG</t>
+  </si>
+  <si>
+    <t>CAB PRO PR - 1312.jpeg</t>
   </si>
   <si>
     <t>CAB PRO PR GM 1.jpg</t>
@@ -3781,46 +3781,46 @@
     <t>CAB CP 15 - 1304.jpg</t>
   </si>
   <si>
-    <t>CAB P12 N - 1308.jpg</t>
-  </si>
-  <si>
-    <t>CAB P8 N - 1309.jpg</t>
+    <t>CAB P12 N - 1308.jpeg</t>
+  </si>
+  <si>
+    <t>CAB P8 N - 1309.jpeg</t>
   </si>
   <si>
     <t>SIE S2 12 - 1163.jpg</t>
   </si>
   <si>
-    <t>C CTR C H CRP - 58.jpg</t>
-  </si>
-  <si>
-    <t>C CTR SBD C - 64.jpg</t>
-  </si>
-  <si>
-    <t>C CTR G H - 60.jpg</t>
-  </si>
-  <si>
-    <t>C CTR 8A G - 1280.jpg</t>
-  </si>
-  <si>
-    <t>C CTR P4 - 62.jpg</t>
-  </si>
-  <si>
-    <t>C CTR 5A G - 53.jpg</t>
-  </si>
-  <si>
-    <t>C CTR 5 G - 1274.jpg</t>
-  </si>
-  <si>
-    <t>C CTR 3 G R - 49.jpg</t>
-  </si>
-  <si>
-    <t>C CTR CR - 59.jpg</t>
-  </si>
-  <si>
-    <t>C CTR GR - 61.jpg</t>
-  </si>
-  <si>
-    <t>C CTR PR - 63.jpg</t>
+    <t>C CTR C H CRP - 58.jpeg</t>
+  </si>
+  <si>
+    <t>C CTR SBD C - 64.jpeg</t>
+  </si>
+  <si>
+    <t>C CTR G H - 60.jpeg</t>
+  </si>
+  <si>
+    <t>C CTR 8A G - 1280.jpeg</t>
+  </si>
+  <si>
+    <t>C CTR P4 - 62.jpeg</t>
+  </si>
+  <si>
+    <t>C CTR 5A G - 53.jpeg</t>
+  </si>
+  <si>
+    <t>C CTR 5 G - 1274.jpeg</t>
+  </si>
+  <si>
+    <t>C CTR 3 G R - 49.jpeg</t>
+  </si>
+  <si>
+    <t>C CTR CR - 59.jpeg</t>
+  </si>
+  <si>
+    <t>C CTR GR - 61.jpeg</t>
+  </si>
+  <si>
+    <t>C CTR PR - 63.jpeg</t>
   </si>
   <si>
     <t>SR PD 350 - 1187.jpg</t>
@@ -3832,25 +3832,25 @@
     <t>CCO TJ 500 - 98.jpg</t>
   </si>
   <si>
-    <t>DES 8PHA 1X100 - 2003.jpg</t>
+    <t>DES 8PHA 1X100 - 2003.jpeg</t>
   </si>
   <si>
     <t>DES 8 PHA 0X75 1.jpg</t>
   </si>
   <si>
-    <t>DES 8PHA 0X75 - 778.jpg</t>
-  </si>
-  <si>
-    <t>DES 8PHA 2X100 - 2004.jpg</t>
-  </si>
-  <si>
-    <t>DES 8PHA 2X150 - 2005.jpg</t>
-  </si>
-  <si>
-    <t>DES 8RA 4X100 - 2021.jpg</t>
-  </si>
-  <si>
-    <t>DES 8RA 5.5X125 - 2022.jpg</t>
+    <t>DES 8PHA 0X75 - 778.jpeg</t>
+  </si>
+  <si>
+    <t>DES 8PHA 2X100 - 2004.jpeg</t>
+  </si>
+  <si>
+    <t>DES 8PHA 2X150 - 2005.jpeg</t>
+  </si>
+  <si>
+    <t>DES 8RA 4X100 - 2021.jpeg</t>
+  </si>
+  <si>
+    <t>DES 8RA 5.5X125 - 2022.jpeg</t>
   </si>
   <si>
     <t>DES 7RA 4X150 1.jpg</t>
@@ -3859,64 +3859,64 @@
     <t>DES 7RA 4X75 1.jpg</t>
   </si>
   <si>
-    <t>DES 7PH 0X50 - 1971.jpg</t>
-  </si>
-  <si>
-    <t>DES 7PH 0X75 - 748.jpg</t>
-  </si>
-  <si>
-    <t>DES 7PH 1X50 - 749.jpg</t>
-  </si>
-  <si>
-    <t>DES 7PH 1X75 - 750.jpg</t>
-  </si>
-  <si>
-    <t>DES 7PH 2X100 - 1975.jpg</t>
-  </si>
-  <si>
-    <t>DES 7PH 2X38 - 752.jpg</t>
-  </si>
-  <si>
-    <t>DES 7PH 3X125 - 1977.jpg</t>
-  </si>
-  <si>
-    <t>DES 7PL 4X100 - 1978.jpg</t>
-  </si>
-  <si>
-    <t>DES 7PL 4X125 - 755.jpg</t>
-  </si>
-  <si>
-    <t>DES 7PL 4X150 - 756.jpg</t>
-  </si>
-  <si>
-    <t>DES 7PL 4X75 - 757.jpg</t>
-  </si>
-  <si>
-    <t>DES 7PL 5X100 - 758.jpg</t>
-  </si>
-  <si>
-    <t>DES 7PL 5X125 - 1983.jpg</t>
-  </si>
-  <si>
-    <t>DES 7PL 5X150 - 1984.jpg</t>
-  </si>
-  <si>
-    <t>DES 7PL 5X75 - 761.jpg</t>
-  </si>
-  <si>
-    <t>DES 7PL 6X100 - 1986.jpg</t>
-  </si>
-  <si>
-    <t>DES 7PL 6X150 - 763.jpg</t>
-  </si>
-  <si>
-    <t>DES 7PL 6X38 - 764.jpg</t>
-  </si>
-  <si>
-    <t>DES 7PL 8X100 - 765.jpg</t>
-  </si>
-  <si>
-    <t>DES 7PL 8X150 - 766.jpg</t>
+    <t>DES 7PH 0X50 - 1971.jpeg</t>
+  </si>
+  <si>
+    <t>DES 7PH 0X75 - 748.jpeg</t>
+  </si>
+  <si>
+    <t>DES 7PH 1X50 - 749.jpeg</t>
+  </si>
+  <si>
+    <t>DES 7PH 1X75 - 750.jpeg</t>
+  </si>
+  <si>
+    <t>DES 7PH 2X100 - 1975.jpeg</t>
+  </si>
+  <si>
+    <t>DES 7PH 2X38 - 752.jpeg</t>
+  </si>
+  <si>
+    <t>DES 7PH 3X125 - 1977.jpeg</t>
+  </si>
+  <si>
+    <t>DES 7PL 4X100 - 1978.jpeg</t>
+  </si>
+  <si>
+    <t>DES 7PL 4X125 - 755.jpeg</t>
+  </si>
+  <si>
+    <t>DES 7PL 4X150 - 756.jpeg</t>
+  </si>
+  <si>
+    <t>DES 7PL 4X75 - 757.jpeg</t>
+  </si>
+  <si>
+    <t>DES 7PL 5X100 - 758.jpeg</t>
+  </si>
+  <si>
+    <t>DES 7PL 5X125 - 1983.jpeg</t>
+  </si>
+  <si>
+    <t>DES 7PL 5X150 - 1984.jpeg</t>
+  </si>
+  <si>
+    <t>DES 7PL 5X75 - 761.jpeg</t>
+  </si>
+  <si>
+    <t>DES 7PL 6X100 - 1986.jpeg</t>
+  </si>
+  <si>
+    <t>DES 7PL 6X150 - 763.jpeg</t>
+  </si>
+  <si>
+    <t>DES 7PL 6X38 - 764.jpeg</t>
+  </si>
+  <si>
+    <t>DES 7PL 8X100 - 765.jpeg</t>
+  </si>
+  <si>
+    <t>DES 7PL 8X150 - 766.jpeg</t>
   </si>
   <si>
     <t>DES 7RT 4X150 1.jpg</t>
@@ -3931,7 +3931,7 @@
     <t>DES 8 ST 6 1.jpg</t>
   </si>
   <si>
-    <t>DES 8A ST 6 1.jpg</t>
+    <t>DES 8A ST 6 1.JPG</t>
   </si>
   <si>
     <t>LLV 7C KIT 5 R 1.jpg</t>
@@ -3943,67 +3943,67 @@
     <t>CH TRX 9 - 1393.jpg</t>
   </si>
   <si>
-    <t>LLV 8VA KIT 7 M - 2197.jpg</t>
+    <t>LLV 8VA KIT 7 M - 2197.jpeg</t>
   </si>
   <si>
     <t>LLC CV 1 12 - 955.jpg</t>
   </si>
   <si>
-    <t>EL PEL 6 A L - 2087.jpg</t>
-  </si>
-  <si>
-    <t>PZA S6 AL6 - 1110.jpg</t>
-  </si>
-  <si>
-    <t>PZA S6 AL7 - 1111.jpg</t>
-  </si>
-  <si>
-    <t>PZA S6 AL7 E - 1112.jpg</t>
-  </si>
-  <si>
-    <t>PZA P8 AL6 - 1101.jpg</t>
-  </si>
-  <si>
-    <t>PZA P8 AL7 - 1102.jpg</t>
-  </si>
-  <si>
-    <t>PZA E AL6 - 1087.jpg</t>
-  </si>
-  <si>
-    <t>PZA E AL7 - 1088.jpg</t>
-  </si>
-  <si>
-    <t>PZA S6 EAL 4.5 - 1113.jpg</t>
-  </si>
-  <si>
-    <t>PZA S6 EAL 4.5F - 1114.jpg</t>
-  </si>
-  <si>
-    <t>PZA S6 AJ10 - 1107.jpg</t>
-  </si>
-  <si>
-    <t>PZA S6 AJ6 - 1108.jpg</t>
-  </si>
-  <si>
-    <t>PZA S6 AJ8 - 1109.jpg</t>
+    <t>EL PEL 6 A L - 2087.jpeg</t>
+  </si>
+  <si>
+    <t>PZA S6 AL6 - 1110.jpeg</t>
+  </si>
+  <si>
+    <t>PZA S6 AL7 - 1111.jpeg</t>
+  </si>
+  <si>
+    <t>PZA S6 AL7 E - 1112.jpeg</t>
+  </si>
+  <si>
+    <t>PZA P8 AL6 - 1101.jpeg</t>
+  </si>
+  <si>
+    <t>PZA P8 AL7 - 1102.jpeg</t>
+  </si>
+  <si>
+    <t>PZA E AL6 - 1087.jpeg</t>
+  </si>
+  <si>
+    <t>PZA E AL7 - 1088.jpeg</t>
+  </si>
+  <si>
+    <t>PZA S6 EAL 4.5 - 1113.jpeg</t>
+  </si>
+  <si>
+    <t>PZA S6 EAL 4.5F - 1114.jpeg</t>
+  </si>
+  <si>
+    <t>PZA S6 AJ10 - 1107.jpeg</t>
+  </si>
+  <si>
+    <t>PZA S6 AJ6 - 1108.jpeg</t>
+  </si>
+  <si>
+    <t>PZA S6 AJ8 - 1109.jpeg</t>
   </si>
   <si>
     <t>PZA FZA 6.5 1.jpg</t>
   </si>
   <si>
-    <t>PZA FZ10 - 1094.jpg</t>
-  </si>
-  <si>
-    <t>PZA S6 EPR 4.5 - 1115.jpg</t>
-  </si>
-  <si>
-    <t>PZA S6 EPS 4.5 - 1116.jpg</t>
-  </si>
-  <si>
-    <t>PZA E PS6 - 1089.jpg</t>
-  </si>
-  <si>
-    <t>PZA E PS8 - 1090.jpg</t>
+    <t>PZA FZ10 - 1094.jpeg</t>
+  </si>
+  <si>
+    <t>PZA S6 EPR 4.5 - 1115.jpeg</t>
+  </si>
+  <si>
+    <t>PZA S6 EPS 4.5 - 1116.jpeg</t>
+  </si>
+  <si>
+    <t>PZA E PS6 - 1089.jpeg</t>
+  </si>
+  <si>
+    <t>PZA E PS8 - 1090.jpeg</t>
   </si>
   <si>
     <t>PZA S6 PL 10 - 1120.jpg</t>
@@ -4012,46 +4012,46 @@
     <t>PZA S6 PL 6 - 1121.jpg</t>
   </si>
   <si>
-    <t>PZA S7 PL 10 P - 1135.jpg</t>
-  </si>
-  <si>
-    <t>PZA S6 PC6 - 1118.jpg</t>
-  </si>
-  <si>
-    <t>PZA S6 PC8 - 1119.jpg</t>
-  </si>
-  <si>
-    <t>PZA S6 PP6 - 1122.jpg</t>
-  </si>
-  <si>
-    <t>PZA S6 PR6 - 1123.jpg</t>
-  </si>
-  <si>
-    <t>PZA S6 PS6 - 1124.jpg</t>
-  </si>
-  <si>
-    <t>PZA S6 PU6 - 1126.jpg</t>
-  </si>
-  <si>
-    <t>PZA S6 PU7 - 1127.jpg</t>
-  </si>
-  <si>
-    <t>PZA S6 PU8 - 1128.jpg</t>
-  </si>
-  <si>
-    <t>PZA E PU6 - 1091.jpg</t>
-  </si>
-  <si>
-    <t>PZA E PU7 - 1092.jpg</t>
-  </si>
-  <si>
-    <t>PZA E PU8 - 1093.jpg</t>
-  </si>
-  <si>
-    <t>PZA S6 EPU 4.5 - 1117.jpg</t>
-  </si>
-  <si>
-    <t>PZA P8 PS6 - 1103.jpg</t>
+    <t>PZA S7 PL 10 P - 1135.jpeg</t>
+  </si>
+  <si>
+    <t>PZA S6 PC6 - 1118.jpeg</t>
+  </si>
+  <si>
+    <t>PZA S6 PC8 - 1119.jpeg</t>
+  </si>
+  <si>
+    <t>PZA S6 PP6 - 1122.jpeg</t>
+  </si>
+  <si>
+    <t>PZA S6 PR6 - 1123.jpeg</t>
+  </si>
+  <si>
+    <t>PZA S6 PS6 - 1124.jpeg</t>
+  </si>
+  <si>
+    <t>PZA S6 PU6 - 1126.jpeg</t>
+  </si>
+  <si>
+    <t>PZA S6 PU7 - 1127.jpeg</t>
+  </si>
+  <si>
+    <t>PZA S6 PU8 - 1128.jpeg</t>
+  </si>
+  <si>
+    <t>PZA E PU6 - 1091.jpeg</t>
+  </si>
+  <si>
+    <t>PZA E PU7 - 1092.jpeg</t>
+  </si>
+  <si>
+    <t>PZA E PU8 - 1093.jpeg</t>
+  </si>
+  <si>
+    <t>PZA S6 EPU 4.5 - 1117.jpeg</t>
+  </si>
+  <si>
+    <t>PZA P8 PS6 - 1103.jpeg</t>
   </si>
   <si>
     <t>PZA S6 SET 3 1.jpg</t>
@@ -4060,34 +4060,34 @@
     <t>PZA S8 SET 3 1.jpg</t>
   </si>
   <si>
-    <t>PZA S6 TN A12 - 1129.jpg</t>
-  </si>
-  <si>
-    <t>PZA S6 TN A9 - 1130.jpg</t>
-  </si>
-  <si>
-    <t>PZA S6 TN AMC12 - 1131.jpg</t>
-  </si>
-  <si>
-    <t>PZA S6 TN AMC9 - 1132.jpg</t>
-  </si>
-  <si>
-    <t>PZA S6 TN7 - 1133.jpg</t>
-  </si>
-  <si>
-    <t>PZA S6 TN8 - 1134.jpg</t>
-  </si>
-  <si>
-    <t>PZA P8 PU6 - 1104.jpg</t>
-  </si>
-  <si>
-    <t>PZA P8 PU7 - 1105.jpg</t>
-  </si>
-  <si>
-    <t>RM 5INT - 1138.jpg</t>
-  </si>
-  <si>
-    <t>PZA AV R - 1086.jpg</t>
+    <t>PZA S6 TN A12 - 1129.jpeg</t>
+  </si>
+  <si>
+    <t>PZA S6 TN A9 - 1130.jpeg</t>
+  </si>
+  <si>
+    <t>PZA S6 TN AMC12 - 1131.jpeg</t>
+  </si>
+  <si>
+    <t>PZA S6 TN AMC9 - 1132.jpeg</t>
+  </si>
+  <si>
+    <t>PZA S6 TN7 - 1133.jpeg</t>
+  </si>
+  <si>
+    <t>PZA S6 TN8 - 1134.jpeg</t>
+  </si>
+  <si>
+    <t>PZA P8 PU6 - 1104.jpeg</t>
+  </si>
+  <si>
+    <t>PZA P8 PU7 - 1105.jpeg</t>
+  </si>
+  <si>
+    <t>RM 5INT - 1138.jpeg</t>
+  </si>
+  <si>
+    <t>PZA AV R - 1086.jpeg</t>
   </si>
   <si>
     <t>CTA MCA 5C 7,5 1.jpg</t>
@@ -4111,37 +4111,37 @@
     <t>CTA MCA7F 8 1.jpg</t>
   </si>
   <si>
-    <t>MBN VEN 1 B - 1013.jpg</t>
-  </si>
-  <si>
-    <t>MBN VEN 12 B - 1014.jpg</t>
-  </si>
-  <si>
-    <t>INF S2 430 MP - 2151.jpg</t>
-  </si>
-  <si>
-    <t>INF S6 272 MA - 2154.jpg</t>
-  </si>
-  <si>
-    <t>INF S6 PIE MA - 10724.jpg</t>
-  </si>
-  <si>
-    <t>INF S2 230 P - 10718.jpg</t>
-  </si>
-  <si>
-    <t>INF S6 225 A - 10720.jpg</t>
-  </si>
-  <si>
-    <t>INF S6 240 TA - 10721.jpg</t>
-  </si>
-  <si>
-    <t>JD S6 PZA BY - 2160.jpg</t>
+    <t>MBN VEN 1 B - 1013.jpeg</t>
+  </si>
+  <si>
+    <t>MBN VEN 12 B - 1014.jpeg</t>
+  </si>
+  <si>
+    <t>INF S2 430 MP - 2151.jpeg</t>
+  </si>
+  <si>
+    <t>INF S6 272 MA - 2154.jpeg</t>
+  </si>
+  <si>
+    <t>INF S6 PIE MA - 10724.jpeg</t>
+  </si>
+  <si>
+    <t>INF S2 230 P - 10718.jpeg</t>
+  </si>
+  <si>
+    <t>INF S6 225 A - 10720.jpeg</t>
+  </si>
+  <si>
+    <t>INF S6 240 TA - 10721.jpeg</t>
+  </si>
+  <si>
+    <t>JD S6 PZA BY - 2160.jpeg</t>
   </si>
   <si>
     <t>JD S8 PZA BY 1.jpg</t>
   </si>
   <si>
-    <t>JD S8 TIJ PD A - 10739.jpg</t>
+    <t>JD S8 TIJ PD A - 10739.jpeg</t>
   </si>
   <si>
     <t>MPX EXA 10 100 - 1026.jpg</t>
@@ -4156,7 +4156,7 @@
     <t>ESP FX 1 - 875.jpg</t>
   </si>
   <si>
-    <t>ESP FX 1,5 - 876.jpg</t>
+    <t>ESP FX 1,5 - 876.jpeg</t>
   </si>
   <si>
     <t>ESP FX 2 - 877.jpg</t>
@@ -4171,7 +4171,7 @@
     <t>PIN S2 12 - 1055.jpg</t>
   </si>
   <si>
-    <t>PIN S2 1 - 1053.jpg</t>
+    <t>PIN S2 1 12 - 1054.jpeg</t>
   </si>
   <si>
     <t>PIN S2 1 12 - 1054.jpg</t>
@@ -4198,16 +4198,16 @@
     <t>C HM G30 UT 17 - 1296.jpg</t>
   </si>
   <si>
-    <t>C PX 2100 - 1301.jpg</t>
+    <t>C PX 2100 1.jpg</t>
   </si>
   <si>
     <t>C PHX 100 1.jpg</t>
   </si>
   <si>
-    <t>C PX 300 - 1302.jpg</t>
-  </si>
-  <si>
-    <t>C PHX 200 R - 1300.jpg</t>
+    <t>C PX 300 1.jpg</t>
+  </si>
+  <si>
+    <t>C PHX 200 R - 1300.jpeg</t>
   </si>
   <si>
     <t>PHB BO C BT 36 1.jpg</t>
@@ -4225,31 +4225,31 @@
     <t>PHB MO 35 1.jpg</t>
   </si>
   <si>
-    <t>GMX ACR 110 B - 2143.jpg</t>
-  </si>
-  <si>
-    <t>GMX CTO 280 G - 2145.jpg</t>
-  </si>
-  <si>
-    <t>GMX ACR 280 B - 2144.jpg</t>
-  </si>
-  <si>
-    <t>GMX J 280 T - 2146.jpg</t>
-  </si>
-  <si>
-    <t>GMX M 280 P - 10716.jpg</t>
-  </si>
-  <si>
-    <t>GMX M 280 N - 10715.jpg</t>
-  </si>
-  <si>
-    <t>EPP PU 300 E - 864.jpg</t>
-  </si>
-  <si>
-    <t>EPP PU 500 E - 865.jpg</t>
-  </si>
-  <si>
-    <t>EPP PU 500 P - 2090.jpg</t>
+    <t>GMX ACR 110 B - 2143.jpeg</t>
+  </si>
+  <si>
+    <t>GMX CTO 280 G - 2145.jpeg</t>
+  </si>
+  <si>
+    <t>GMX ACR 280 B - 2144.jpeg</t>
+  </si>
+  <si>
+    <t>GMX J 280 T - 2146.jpeg</t>
+  </si>
+  <si>
+    <t>GMX M 280 P - 10716.jpeg</t>
+  </si>
+  <si>
+    <t>GMX M 280 N - 10715.jpeg</t>
+  </si>
+  <si>
+    <t>EPP PU 300 E - 864.jpeg</t>
+  </si>
+  <si>
+    <t>EPP PU 500 E - 865.jpeg</t>
+  </si>
+  <si>
+    <t>EPP PU 500 P - 2090.jpeg</t>
   </si>
   <si>
     <t>EPP PU 750 E 1.jpg</t>
@@ -4258,52 +4258,46 @@
     <t>EPP PU 750 P 1.jpg</t>
   </si>
   <si>
-    <t>PST GR - 1075.jpg</t>
+    <t>PST GR - 1075.jpeg</t>
   </si>
   <si>
     <t>PST PL 800 - 1078.jpg</t>
   </si>
   <si>
-    <t>GAS 125 E 1.jpg</t>
-  </si>
-  <si>
     <t>GAS 125 1.jpg</t>
   </si>
   <si>
     <t>GAS 25 - 2122.jpg</t>
   </si>
   <si>
-    <t>GAS 50 - 2123.jpg</t>
-  </si>
-  <si>
-    <t>PBD 400 B - 1047.jpg</t>
+    <t>GAS 50 1.jpg</t>
+  </si>
+  <si>
+    <t>PBD 400 B - 1047.jpeg</t>
   </si>
   <si>
     <t>PBD 400 - 1046.jpg</t>
   </si>
   <si>
-    <t>PBD 25 T 1.jpg</t>
-  </si>
-  <si>
-    <t>SMZ 50 A - 1181.jpg</t>
-  </si>
-  <si>
-    <t>SMZ 300 A - 1180.jpg</t>
+    <t>SMZ 50 A - 1181.jpeg</t>
+  </si>
+  <si>
+    <t>SMZ 300 A - 1180.jpeg</t>
   </si>
   <si>
     <t>PBD P 25 T 1.jpg</t>
   </si>
   <si>
-    <t>PBD P 50 - 1052.jpg</t>
-  </si>
-  <si>
-    <t>PSC 310 A - 1074.jpg</t>
+    <t>PBD P 50 1.jpg</t>
+  </si>
+  <si>
+    <t>PSC 310 A - 1074.jpeg</t>
   </si>
   <si>
     <t>GFX 25 - 2124.jpg</t>
   </si>
   <si>
-    <t>GFX C 280 T - 2129.jpg</t>
+    <t>GFX C 280 T - 2129.jpeg</t>
   </si>
   <si>
     <t>GFX AT S5 280 R 1.jpg</t>
@@ -4312,46 +4306,46 @@
     <t>GFX A S5 280 T 1.jpg</t>
   </si>
   <si>
-    <t>GFX J 110 R - 2130.jpg</t>
-  </si>
-  <si>
-    <t>GFX J 60 R - 2132.jpg</t>
-  </si>
-  <si>
-    <t>GFX C 110 T - 2128.jpg</t>
+    <t>GFX J 110 R - 2130.jpeg</t>
+  </si>
+  <si>
+    <t>GFX J 60 R - 2132.jpeg</t>
+  </si>
+  <si>
+    <t>GFX C 110 T - 2128.jpeg</t>
   </si>
   <si>
     <t>GFX N S5 280 T 1.jpg</t>
   </si>
   <si>
-    <t>GFX U 280 B - 2136.jpg</t>
-  </si>
-  <si>
-    <t>GFX U 280 N - 2137.jpg</t>
-  </si>
-  <si>
-    <t>GFX U 280 T - 2138.jpg</t>
-  </si>
-  <si>
-    <t>GFX U 110 B - 2133.jpg</t>
-  </si>
-  <si>
-    <t>GFX U 110 T - 2135.jpg</t>
-  </si>
-  <si>
-    <t>GFX U 60 B - 2139.jpg</t>
-  </si>
-  <si>
-    <t>GFX U 60 N - 2140.jpg</t>
-  </si>
-  <si>
-    <t>GFX U 60 T - 2141.jpg</t>
+    <t>GFX U 280 B - 2136.jpeg</t>
+  </si>
+  <si>
+    <t>GFX U 280 N - 2137.jpeg</t>
+  </si>
+  <si>
+    <t>GFX U 280 T - 2138.jpeg</t>
+  </si>
+  <si>
+    <t>GFX U 110 B - 2133.jpeg</t>
+  </si>
+  <si>
+    <t>GFX U 110 T - 2135.jpeg</t>
+  </si>
+  <si>
+    <t>GFX U 60 B - 2139.jpeg</t>
+  </si>
+  <si>
+    <t>GFX U 60 N - 2140.jpeg</t>
+  </si>
+  <si>
+    <t>GFX U 60 T - 2141.jpeg</t>
   </si>
   <si>
     <t>RTR ESP 1.jpg</t>
   </si>
   <si>
-    <t>KIT PRB - 2175.jpg</t>
+    <t>KIT PRB - 2175.jpeg</t>
   </si>
   <si>
     <t>KIT R OP 1.jpg</t>
@@ -4360,25 +4354,25 @@
     <t>AFX VA 2 - 1240.jpg</t>
   </si>
   <si>
-    <t>AFX CA 25X5 N 1.jpg</t>
+    <t>AFX CA 25X5 N 10.jpg</t>
   </si>
   <si>
     <t>AFX W 16 - 1242.jpg</t>
   </si>
   <si>
-    <t>AFX W R2 - 1243.jpg</t>
-  </si>
-  <si>
-    <t>AFX S E - 1238.jpg</t>
-  </si>
-  <si>
-    <t>AFX P66 BO 1.jpg</t>
-  </si>
-  <si>
-    <t>AFX P54 BO 1.jpg</t>
-  </si>
-  <si>
-    <t>AFX P54 TO - 1.jpg</t>
+    <t>AFX W R2 - 1243.jpeg</t>
+  </si>
+  <si>
+    <t>AFX S E - 1238.jpeg</t>
+  </si>
+  <si>
+    <t>AFX P66 BO 1.jpeg</t>
+  </si>
+  <si>
+    <t>AFX P54 BO 1.jpeg</t>
+  </si>
+  <si>
+    <t>AFX P54 TO - 1.jpeg</t>
   </si>
   <si>
     <t>AFX P35 BO 1.jpg</t>
@@ -4387,16 +4381,16 @@
     <t>AFX P35 TO.jpg</t>
   </si>
   <si>
-    <t>AFX P49 AR 1.jpg</t>
-  </si>
-  <si>
-    <t>AFX P18 AR - 2451.jpg</t>
+    <t>AFX P49 AR 1.jpeg</t>
+  </si>
+  <si>
+    <t>AFX P18 AR - 2451.jpeg</t>
   </si>
   <si>
     <t>AFX PEA 4 T 1.jpg</t>
   </si>
   <si>
-    <t>AFX RUE 4 AI - 1237.jpg</t>
+    <t>AFX RUE 4 AI - 1237.jpeg</t>
   </si>
   <si>
     <t>AFX PC 1 20 1.jpg</t>
@@ -4414,49 +4408,49 @@
     <t>AFX MV 1X1,2 N 1.jpg</t>
   </si>
   <si>
-    <t>AFX P R33 B 1.jpg</t>
-  </si>
-  <si>
-    <t>AFX P R80 BO 1.jpg</t>
-  </si>
-  <si>
-    <t>AFX P R80 TO 1.jpg</t>
+    <t>AFX P R33 B 1.JPG</t>
+  </si>
+  <si>
+    <t>AFX P R80 BO 1.JPG</t>
+  </si>
+  <si>
+    <t>AFX P R80 TO 1.JPG</t>
   </si>
   <si>
     <t>AFX ZP 7X5 B 1.jpg</t>
   </si>
   <si>
-    <t>TPC F 20 M - 1195.jpg</t>
-  </si>
-  <si>
-    <t>TPC F 30 M - 1196.jpg</t>
-  </si>
-  <si>
-    <t>TPR F 20 M - 1199.jpg</t>
-  </si>
-  <si>
-    <t>TPR F 30 M - 1200.jpg</t>
-  </si>
-  <si>
-    <t>TPC A 18 T - 1193.jpg</t>
-  </si>
-  <si>
-    <t>TPR BC - 1198.jpg</t>
-  </si>
-  <si>
-    <t>TPR SM - 1201.jpg</t>
-  </si>
-  <si>
-    <t>TPC BC - 1194.jpg</t>
-  </si>
-  <si>
-    <t>TPC SM - 1197.jpg</t>
+    <t>TPC F 20 M - 1195.jpeg</t>
+  </si>
+  <si>
+    <t>TPC F 30 M - 1196.jpeg</t>
+  </si>
+  <si>
+    <t>TPR F 20 M - 1199.jpeg</t>
+  </si>
+  <si>
+    <t>TPR F 30 M - 1200.jpeg</t>
+  </si>
+  <si>
+    <t>TPC A 18 T - 1193.jpeg</t>
+  </si>
+  <si>
+    <t>TPR BC - 1198.jpeg</t>
+  </si>
+  <si>
+    <t>TPR SM - 1201.jpeg</t>
+  </si>
+  <si>
+    <t>TPC BC - 1194.jpeg</t>
+  </si>
+  <si>
+    <t>TPC SM - 1197.jpeg</t>
+  </si>
+  <si>
+    <t>EXACTO</t>
   </si>
   <si>
     <t>NO</t>
-  </si>
-  <si>
-    <t>EXACTO</t>
   </si>
   <si>
     <t>SIN_BARRA</t>
@@ -4852,7 +4846,7 @@
         <v>1086</v>
       </c>
       <c r="I2" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -4881,7 +4875,7 @@
         <v>1087</v>
       </c>
       <c r="I3" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -4910,7 +4904,7 @@
         <v>1088</v>
       </c>
       <c r="I4" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -4939,7 +4933,7 @@
         <v>1089</v>
       </c>
       <c r="I5" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -4968,7 +4962,7 @@
         <v>1090</v>
       </c>
       <c r="I6" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -4997,7 +4991,7 @@
         <v>1091</v>
       </c>
       <c r="I7" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -5026,7 +5020,7 @@
         <v>1092</v>
       </c>
       <c r="I8" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -5055,7 +5049,7 @@
         <v>1093</v>
       </c>
       <c r="I9" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -5084,7 +5078,7 @@
         <v>1094</v>
       </c>
       <c r="I10" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5110,7 +5104,7 @@
         <v>1095</v>
       </c>
       <c r="I11" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -5139,7 +5133,7 @@
         <v>1096</v>
       </c>
       <c r="I12" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -5168,7 +5162,7 @@
         <v>1097</v>
       </c>
       <c r="I13" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -5197,7 +5191,7 @@
         <v>1098</v>
       </c>
       <c r="I14" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -5226,7 +5220,7 @@
         <v>1099</v>
       </c>
       <c r="I15" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -5255,7 +5249,7 @@
         <v>1100</v>
       </c>
       <c r="I16" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -5284,7 +5278,7 @@
         <v>1101</v>
       </c>
       <c r="I17" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -5313,7 +5307,7 @@
         <v>1102</v>
       </c>
       <c r="I18" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -5342,7 +5336,7 @@
         <v>1103</v>
       </c>
       <c r="I19" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -5371,7 +5365,7 @@
         <v>1104</v>
       </c>
       <c r="I20" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -5400,7 +5394,7 @@
         <v>1105</v>
       </c>
       <c r="I21" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -5429,7 +5423,7 @@
         <v>1106</v>
       </c>
       <c r="I22" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -5458,7 +5452,7 @@
         <v>1107</v>
       </c>
       <c r="I23" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -5487,7 +5481,7 @@
         <v>1108</v>
       </c>
       <c r="I24" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -5516,7 +5510,7 @@
         <v>1109</v>
       </c>
       <c r="I25" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -5545,7 +5539,7 @@
         <v>1110</v>
       </c>
       <c r="I26" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -5574,7 +5568,7 @@
         <v>1111</v>
       </c>
       <c r="I27" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -5603,7 +5597,7 @@
         <v>1112</v>
       </c>
       <c r="I28" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -5632,7 +5626,7 @@
         <v>1113</v>
       </c>
       <c r="I29" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -5661,7 +5655,7 @@
         <v>1114</v>
       </c>
       <c r="I30" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -5690,7 +5684,7 @@
         <v>1115</v>
       </c>
       <c r="I31" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -5719,7 +5713,7 @@
         <v>1116</v>
       </c>
       <c r="I32" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -5748,7 +5742,7 @@
         <v>1117</v>
       </c>
       <c r="I33" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -5777,7 +5771,7 @@
         <v>1118</v>
       </c>
       <c r="I34" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -5806,7 +5800,7 @@
         <v>1119</v>
       </c>
       <c r="I35" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -5835,7 +5829,7 @@
         <v>1120</v>
       </c>
       <c r="I36" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -5864,7 +5858,7 @@
         <v>1121</v>
       </c>
       <c r="I37" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -5893,7 +5887,7 @@
         <v>1122</v>
       </c>
       <c r="I38" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -5922,7 +5916,7 @@
         <v>1123</v>
       </c>
       <c r="I39" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -5951,7 +5945,7 @@
         <v>1124</v>
       </c>
       <c r="I40" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -5980,7 +5974,7 @@
         <v>1125</v>
       </c>
       <c r="I41" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -6009,7 +6003,7 @@
         <v>1126</v>
       </c>
       <c r="I42" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -6038,7 +6032,7 @@
         <v>1127</v>
       </c>
       <c r="I43" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -6067,7 +6061,7 @@
         <v>1128</v>
       </c>
       <c r="I44" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -6093,7 +6087,7 @@
         <v>1129</v>
       </c>
       <c r="I45" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -6122,7 +6116,7 @@
         <v>1130</v>
       </c>
       <c r="I46" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -6151,7 +6145,7 @@
         <v>1131</v>
       </c>
       <c r="I47" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -6180,7 +6174,7 @@
         <v>1132</v>
       </c>
       <c r="I48" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -6209,7 +6203,7 @@
         <v>1133</v>
       </c>
       <c r="I49" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -6238,7 +6232,7 @@
         <v>1134</v>
       </c>
       <c r="I50" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -6267,7 +6261,7 @@
         <v>1135</v>
       </c>
       <c r="I51" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -6296,7 +6290,7 @@
         <v>1136</v>
       </c>
       <c r="I52" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -6325,7 +6319,7 @@
         <v>1137</v>
       </c>
       <c r="I53" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -6354,7 +6348,7 @@
         <v>1138</v>
       </c>
       <c r="I54" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -6383,7 +6377,7 @@
         <v>1139</v>
       </c>
       <c r="I55" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -6412,7 +6406,7 @@
         <v>1140</v>
       </c>
       <c r="I56" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -6441,7 +6435,7 @@
         <v>1141</v>
       </c>
       <c r="I57" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -6470,7 +6464,7 @@
         <v>1142</v>
       </c>
       <c r="I58" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -6499,7 +6493,7 @@
         <v>1143</v>
       </c>
       <c r="I59" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -6528,7 +6522,7 @@
         <v>1144</v>
       </c>
       <c r="I60" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -6557,7 +6551,7 @@
         <v>1145</v>
       </c>
       <c r="I61" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -6586,7 +6580,7 @@
         <v>1146</v>
       </c>
       <c r="I62" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -6615,7 +6609,7 @@
         <v>1147</v>
       </c>
       <c r="I63" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -6644,7 +6638,7 @@
         <v>1148</v>
       </c>
       <c r="I64" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -6673,7 +6667,7 @@
         <v>1149</v>
       </c>
       <c r="I65" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -6702,7 +6696,7 @@
         <v>1150</v>
       </c>
       <c r="I66" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -6731,7 +6725,7 @@
         <v>1151</v>
       </c>
       <c r="I67" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -6760,7 +6754,7 @@
         <v>1152</v>
       </c>
       <c r="I68" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -6789,7 +6783,7 @@
         <v>1153</v>
       </c>
       <c r="I69" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -6818,7 +6812,7 @@
         <v>1154</v>
       </c>
       <c r="I70" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -6847,7 +6841,7 @@
         <v>1155</v>
       </c>
       <c r="I71" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -6876,7 +6870,7 @@
         <v>1156</v>
       </c>
       <c r="I72" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -6905,7 +6899,7 @@
         <v>1157</v>
       </c>
       <c r="I73" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -6934,7 +6928,7 @@
         <v>1158</v>
       </c>
       <c r="I74" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -6963,7 +6957,7 @@
         <v>1159</v>
       </c>
       <c r="I75" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -6992,7 +6986,7 @@
         <v>1160</v>
       </c>
       <c r="I76" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -7021,7 +7015,7 @@
         <v>1161</v>
       </c>
       <c r="I77" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -7050,7 +7044,7 @@
         <v>1162</v>
       </c>
       <c r="I78" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -7079,7 +7073,7 @@
         <v>1163</v>
       </c>
       <c r="I79" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -7108,7 +7102,7 @@
         <v>1164</v>
       </c>
       <c r="I80" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -7137,7 +7131,7 @@
         <v>1165</v>
       </c>
       <c r="I81" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -7166,7 +7160,7 @@
         <v>1166</v>
       </c>
       <c r="I82" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -7195,7 +7189,7 @@
         <v>1167</v>
       </c>
       <c r="I83" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -7224,7 +7218,7 @@
         <v>1168</v>
       </c>
       <c r="I84" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -7253,7 +7247,7 @@
         <v>1169</v>
       </c>
       <c r="I85" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -7282,7 +7276,7 @@
         <v>1170</v>
       </c>
       <c r="I86" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -7311,7 +7305,7 @@
         <v>1171</v>
       </c>
       <c r="I87" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -7340,7 +7334,7 @@
         <v>1172</v>
       </c>
       <c r="I88" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -7369,7 +7363,7 @@
         <v>1173</v>
       </c>
       <c r="I89" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -7398,7 +7392,7 @@
         <v>1174</v>
       </c>
       <c r="I90" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -7427,7 +7421,7 @@
         <v>1175</v>
       </c>
       <c r="I91" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -7456,7 +7450,7 @@
         <v>1176</v>
       </c>
       <c r="I92" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -7485,7 +7479,7 @@
         <v>1177</v>
       </c>
       <c r="I93" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -7514,7 +7508,7 @@
         <v>1178</v>
       </c>
       <c r="I94" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -7543,7 +7537,7 @@
         <v>1179</v>
       </c>
       <c r="I95" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -7572,7 +7566,7 @@
         <v>1180</v>
       </c>
       <c r="I96" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -7601,7 +7595,7 @@
         <v>1181</v>
       </c>
       <c r="I97" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -7630,7 +7624,7 @@
         <v>1182</v>
       </c>
       <c r="I98" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -7659,7 +7653,7 @@
         <v>1183</v>
       </c>
       <c r="I99" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -7688,7 +7682,7 @@
         <v>1184</v>
       </c>
       <c r="I100" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -7717,7 +7711,7 @@
         <v>1185</v>
       </c>
       <c r="I101" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -7746,7 +7740,7 @@
         <v>1186</v>
       </c>
       <c r="I102" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -7775,7 +7769,7 @@
         <v>1187</v>
       </c>
       <c r="I103" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -7804,7 +7798,7 @@
         <v>1188</v>
       </c>
       <c r="I104" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -7833,7 +7827,7 @@
         <v>1189</v>
       </c>
       <c r="I105" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -7862,7 +7856,7 @@
         <v>1190</v>
       </c>
       <c r="I106" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -7891,7 +7885,7 @@
         <v>1191</v>
       </c>
       <c r="I107" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -7920,7 +7914,7 @@
         <v>1192</v>
       </c>
       <c r="I108" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -7949,7 +7943,7 @@
         <v>1192</v>
       </c>
       <c r="I109" t="s">
-        <v>1482</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -7978,7 +7972,7 @@
         <v>1193</v>
       </c>
       <c r="I110" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -8007,7 +8001,7 @@
         <v>1194</v>
       </c>
       <c r="I111" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -8036,7 +8030,7 @@
         <v>1195</v>
       </c>
       <c r="I112" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -8065,7 +8059,7 @@
         <v>1196</v>
       </c>
       <c r="I113" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -8094,7 +8088,7 @@
         <v>1197</v>
       </c>
       <c r="I114" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -8123,7 +8117,7 @@
         <v>1198</v>
       </c>
       <c r="I115" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -8152,7 +8146,7 @@
         <v>1199</v>
       </c>
       <c r="I116" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -8181,7 +8175,7 @@
         <v>1200</v>
       </c>
       <c r="I117" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -8210,7 +8204,7 @@
         <v>1201</v>
       </c>
       <c r="I118" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -8239,7 +8233,7 @@
         <v>1202</v>
       </c>
       <c r="I119" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -8268,7 +8262,7 @@
         <v>1203</v>
       </c>
       <c r="I120" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -8297,7 +8291,7 @@
         <v>1204</v>
       </c>
       <c r="I121" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -8326,7 +8320,7 @@
         <v>1205</v>
       </c>
       <c r="I122" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -8355,7 +8349,7 @@
         <v>1206</v>
       </c>
       <c r="I123" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -8384,7 +8378,7 @@
         <v>1207</v>
       </c>
       <c r="I124" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -8410,7 +8404,7 @@
         <v>1208</v>
       </c>
       <c r="I125" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -8439,7 +8433,7 @@
         <v>1209</v>
       </c>
       <c r="I126" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -8468,7 +8462,7 @@
         <v>1210</v>
       </c>
       <c r="I127" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -8497,7 +8491,7 @@
         <v>1211</v>
       </c>
       <c r="I128" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -8526,7 +8520,7 @@
         <v>1212</v>
       </c>
       <c r="I129" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -8555,7 +8549,7 @@
         <v>1213</v>
       </c>
       <c r="I130" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -8584,7 +8578,7 @@
         <v>1214</v>
       </c>
       <c r="I131" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -8613,7 +8607,7 @@
         <v>1215</v>
       </c>
       <c r="I132" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -8642,7 +8636,7 @@
         <v>1216</v>
       </c>
       <c r="I133" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -8671,7 +8665,7 @@
         <v>1217</v>
       </c>
       <c r="I134" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -8700,7 +8694,7 @@
         <v>1218</v>
       </c>
       <c r="I135" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -8729,7 +8723,7 @@
         <v>1219</v>
       </c>
       <c r="I136" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -8758,7 +8752,7 @@
         <v>1220</v>
       </c>
       <c r="I137" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -8787,7 +8781,7 @@
         <v>1221</v>
       </c>
       <c r="I138" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -8816,7 +8810,7 @@
         <v>1222</v>
       </c>
       <c r="I139" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -8845,7 +8839,7 @@
         <v>1223</v>
       </c>
       <c r="I140" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -8874,7 +8868,7 @@
         <v>1224</v>
       </c>
       <c r="I141" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -8903,7 +8897,7 @@
         <v>1225</v>
       </c>
       <c r="I142" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -8932,7 +8926,7 @@
         <v>1226</v>
       </c>
       <c r="I143" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -8961,7 +8955,7 @@
         <v>1227</v>
       </c>
       <c r="I144" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -8990,7 +8984,7 @@
         <v>1228</v>
       </c>
       <c r="I145" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -9019,7 +9013,7 @@
         <v>1229</v>
       </c>
       <c r="I146" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -9048,7 +9042,7 @@
         <v>1230</v>
       </c>
       <c r="I147" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -9077,7 +9071,7 @@
         <v>1231</v>
       </c>
       <c r="I148" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -9106,7 +9100,7 @@
         <v>1232</v>
       </c>
       <c r="I149" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -9135,7 +9129,7 @@
         <v>1233</v>
       </c>
       <c r="I150" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -9164,7 +9158,7 @@
         <v>1234</v>
       </c>
       <c r="I151" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -9193,7 +9187,7 @@
         <v>1235</v>
       </c>
       <c r="I152" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -9222,7 +9216,7 @@
         <v>1236</v>
       </c>
       <c r="I153" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -9251,7 +9245,7 @@
         <v>1237</v>
       </c>
       <c r="I154" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -9280,7 +9274,7 @@
         <v>1238</v>
       </c>
       <c r="I155" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -9309,7 +9303,7 @@
         <v>1239</v>
       </c>
       <c r="I156" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -9338,7 +9332,7 @@
         <v>1240</v>
       </c>
       <c r="I157" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -9367,7 +9361,7 @@
         <v>1241</v>
       </c>
       <c r="I158" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -9396,7 +9390,7 @@
         <v>1242</v>
       </c>
       <c r="I159" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -9425,7 +9419,7 @@
         <v>1243</v>
       </c>
       <c r="I160" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -9454,7 +9448,7 @@
         <v>1244</v>
       </c>
       <c r="I161" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -9483,7 +9477,7 @@
         <v>1245</v>
       </c>
       <c r="I162" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -9512,7 +9506,7 @@
         <v>1246</v>
       </c>
       <c r="I163" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -9541,7 +9535,7 @@
         <v>1247</v>
       </c>
       <c r="I164" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -9570,7 +9564,7 @@
         <v>1248</v>
       </c>
       <c r="I165" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -9599,7 +9593,7 @@
         <v>1249</v>
       </c>
       <c r="I166" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -9628,7 +9622,7 @@
         <v>1250</v>
       </c>
       <c r="I167" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -9657,7 +9651,7 @@
         <v>1251</v>
       </c>
       <c r="I168" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -9686,7 +9680,7 @@
         <v>1252</v>
       </c>
       <c r="I169" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -9715,7 +9709,7 @@
         <v>1253</v>
       </c>
       <c r="I170" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -9744,7 +9738,7 @@
         <v>1254</v>
       </c>
       <c r="I171" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="172" spans="1:9">
@@ -9773,7 +9767,7 @@
         <v>1255</v>
       </c>
       <c r="I172" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="173" spans="1:9">
@@ -9802,7 +9796,7 @@
         <v>1256</v>
       </c>
       <c r="I173" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="174" spans="1:9">
@@ -9831,7 +9825,7 @@
         <v>1257</v>
       </c>
       <c r="I174" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="175" spans="1:9">
@@ -9860,7 +9854,7 @@
         <v>1258</v>
       </c>
       <c r="I175" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="176" spans="1:9">
@@ -9889,7 +9883,7 @@
         <v>1259</v>
       </c>
       <c r="I176" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="177" spans="1:9">
@@ -9918,7 +9912,7 @@
         <v>1260</v>
       </c>
       <c r="I177" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="178" spans="1:9">
@@ -9947,7 +9941,7 @@
         <v>1261</v>
       </c>
       <c r="I178" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="179" spans="1:9">
@@ -9976,7 +9970,7 @@
         <v>1262</v>
       </c>
       <c r="I179" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="180" spans="1:9">
@@ -10005,7 +9999,7 @@
         <v>1263</v>
       </c>
       <c r="I180" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="181" spans="1:9">
@@ -10034,7 +10028,7 @@
         <v>1264</v>
       </c>
       <c r="I181" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="182" spans="1:9">
@@ -10063,7 +10057,7 @@
         <v>1265</v>
       </c>
       <c r="I182" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="183" spans="1:9">
@@ -10092,7 +10086,7 @@
         <v>1266</v>
       </c>
       <c r="I183" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="184" spans="1:9">
@@ -10121,7 +10115,7 @@
         <v>1267</v>
       </c>
       <c r="I184" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="185" spans="1:9">
@@ -10150,7 +10144,7 @@
         <v>1268</v>
       </c>
       <c r="I185" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="186" spans="1:9">
@@ -10179,7 +10173,7 @@
         <v>1269</v>
       </c>
       <c r="I186" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="187" spans="1:9">
@@ -10208,7 +10202,7 @@
         <v>1270</v>
       </c>
       <c r="I187" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="188" spans="1:9">
@@ -10237,7 +10231,7 @@
         <v>1271</v>
       </c>
       <c r="I188" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="189" spans="1:9">
@@ -10266,7 +10260,7 @@
         <v>1272</v>
       </c>
       <c r="I189" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="190" spans="1:9">
@@ -10295,7 +10289,7 @@
         <v>1273</v>
       </c>
       <c r="I190" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="191" spans="1:9">
@@ -10324,7 +10318,7 @@
         <v>1274</v>
       </c>
       <c r="I191" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="192" spans="1:9">
@@ -10353,7 +10347,7 @@
         <v>1275</v>
       </c>
       <c r="I192" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="193" spans="1:9">
@@ -10382,7 +10376,7 @@
         <v>1276</v>
       </c>
       <c r="I193" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="194" spans="1:9">
@@ -10411,7 +10405,7 @@
         <v>1277</v>
       </c>
       <c r="I194" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="195" spans="1:9">
@@ -10440,7 +10434,7 @@
         <v>1278</v>
       </c>
       <c r="I195" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="196" spans="1:9">
@@ -10469,7 +10463,7 @@
         <v>1279</v>
       </c>
       <c r="I196" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="197" spans="1:9">
@@ -10498,7 +10492,7 @@
         <v>1280</v>
       </c>
       <c r="I197" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -10527,7 +10521,7 @@
         <v>1281</v>
       </c>
       <c r="I198" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -10556,7 +10550,7 @@
         <v>1282</v>
       </c>
       <c r="I199" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="200" spans="1:9">
@@ -10585,7 +10579,7 @@
         <v>1283</v>
       </c>
       <c r="I200" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -10614,7 +10608,7 @@
         <v>1284</v>
       </c>
       <c r="I201" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -10643,7 +10637,7 @@
         <v>1285</v>
       </c>
       <c r="I202" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -10672,7 +10666,7 @@
         <v>1286</v>
       </c>
       <c r="I203" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -10701,7 +10695,7 @@
         <v>1287</v>
       </c>
       <c r="I204" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -10730,7 +10724,7 @@
         <v>1288</v>
       </c>
       <c r="I205" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -10759,7 +10753,7 @@
         <v>1289</v>
       </c>
       <c r="I206" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="207" spans="1:9">
@@ -10788,7 +10782,7 @@
         <v>1290</v>
       </c>
       <c r="I207" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -10817,7 +10811,7 @@
         <v>1291</v>
       </c>
       <c r="I208" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="209" spans="1:9">
@@ -10846,7 +10840,7 @@
         <v>1292</v>
       </c>
       <c r="I209" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="210" spans="1:9">
@@ -10875,7 +10869,7 @@
         <v>1293</v>
       </c>
       <c r="I210" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="211" spans="1:9">
@@ -10904,7 +10898,7 @@
         <v>1294</v>
       </c>
       <c r="I211" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="212" spans="1:9">
@@ -10933,7 +10927,7 @@
         <v>1295</v>
       </c>
       <c r="I212" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="213" spans="1:9">
@@ -10962,7 +10956,7 @@
         <v>1296</v>
       </c>
       <c r="I213" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="214" spans="1:9">
@@ -10991,7 +10985,7 @@
         <v>1297</v>
       </c>
       <c r="I214" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="215" spans="1:9">
@@ -11020,7 +11014,7 @@
         <v>1298</v>
       </c>
       <c r="I215" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="216" spans="1:9">
@@ -11049,7 +11043,7 @@
         <v>1299</v>
       </c>
       <c r="I216" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="217" spans="1:9">
@@ -11078,7 +11072,7 @@
         <v>1300</v>
       </c>
       <c r="I217" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="218" spans="1:9">
@@ -11107,7 +11101,7 @@
         <v>1301</v>
       </c>
       <c r="I218" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="219" spans="1:9">
@@ -11136,7 +11130,7 @@
         <v>1302</v>
       </c>
       <c r="I219" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="220" spans="1:9">
@@ -11165,7 +11159,7 @@
         <v>1303</v>
       </c>
       <c r="I220" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="221" spans="1:9">
@@ -11194,7 +11188,7 @@
         <v>1304</v>
       </c>
       <c r="I221" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="222" spans="1:9">
@@ -11223,7 +11217,7 @@
         <v>1305</v>
       </c>
       <c r="I222" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -11252,7 +11246,7 @@
         <v>1306</v>
       </c>
       <c r="I223" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="224" spans="1:9">
@@ -11281,7 +11275,7 @@
         <v>1307</v>
       </c>
       <c r="I224" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="225" spans="1:9">
@@ -11310,7 +11304,7 @@
         <v>1308</v>
       </c>
       <c r="I225" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="226" spans="1:9">
@@ -11339,7 +11333,7 @@
         <v>1309</v>
       </c>
       <c r="I226" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="227" spans="1:9">
@@ -11368,7 +11362,7 @@
         <v>1310</v>
       </c>
       <c r="I227" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="228" spans="1:9">
@@ -11397,7 +11391,7 @@
         <v>1311</v>
       </c>
       <c r="I228" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="229" spans="1:9">
@@ -11426,7 +11420,7 @@
         <v>1312</v>
       </c>
       <c r="I229" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="230" spans="1:9">
@@ -11455,7 +11449,7 @@
         <v>1313</v>
       </c>
       <c r="I230" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="231" spans="1:9">
@@ -11484,7 +11478,7 @@
         <v>1314</v>
       </c>
       <c r="I231" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="232" spans="1:9">
@@ -11513,7 +11507,7 @@
         <v>1315</v>
       </c>
       <c r="I232" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="233" spans="1:9">
@@ -11542,7 +11536,7 @@
         <v>1316</v>
       </c>
       <c r="I233" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="234" spans="1:9">
@@ -11571,7 +11565,7 @@
         <v>1317</v>
       </c>
       <c r="I234" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="235" spans="1:9">
@@ -11600,7 +11594,7 @@
         <v>1318</v>
       </c>
       <c r="I235" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="236" spans="1:9">
@@ -11629,7 +11623,7 @@
         <v>1319</v>
       </c>
       <c r="I236" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="237" spans="1:9">
@@ -11658,7 +11652,7 @@
         <v>1320</v>
       </c>
       <c r="I237" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="238" spans="1:9">
@@ -11687,7 +11681,7 @@
         <v>1321</v>
       </c>
       <c r="I238" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="239" spans="1:9">
@@ -11716,7 +11710,7 @@
         <v>1322</v>
       </c>
       <c r="I239" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="240" spans="1:9">
@@ -11745,7 +11739,7 @@
         <v>1323</v>
       </c>
       <c r="I240" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="241" spans="1:9">
@@ -11774,7 +11768,7 @@
         <v>1324</v>
       </c>
       <c r="I241" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="242" spans="1:9">
@@ -11803,7 +11797,7 @@
         <v>1325</v>
       </c>
       <c r="I242" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="243" spans="1:9">
@@ -11832,7 +11826,7 @@
         <v>1326</v>
       </c>
       <c r="I243" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="244" spans="1:9">
@@ -11861,7 +11855,7 @@
         <v>1327</v>
       </c>
       <c r="I244" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="245" spans="1:9">
@@ -11890,7 +11884,7 @@
         <v>1328</v>
       </c>
       <c r="I245" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="246" spans="1:9">
@@ -11919,7 +11913,7 @@
         <v>1329</v>
       </c>
       <c r="I246" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="247" spans="1:9">
@@ -11948,7 +11942,7 @@
         <v>1330</v>
       </c>
       <c r="I247" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="248" spans="1:9">
@@ -11977,7 +11971,7 @@
         <v>1331</v>
       </c>
       <c r="I248" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="249" spans="1:9">
@@ -12006,7 +12000,7 @@
         <v>1332</v>
       </c>
       <c r="I249" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="250" spans="1:9">
@@ -12035,7 +12029,7 @@
         <v>1333</v>
       </c>
       <c r="I250" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="251" spans="1:9">
@@ -12064,7 +12058,7 @@
         <v>1334</v>
       </c>
       <c r="I251" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="252" spans="1:9">
@@ -12093,7 +12087,7 @@
         <v>1335</v>
       </c>
       <c r="I252" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="253" spans="1:9">
@@ -12122,7 +12116,7 @@
         <v>1336</v>
       </c>
       <c r="I253" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="254" spans="1:9">
@@ -12151,7 +12145,7 @@
         <v>1337</v>
       </c>
       <c r="I254" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="255" spans="1:9">
@@ -12180,7 +12174,7 @@
         <v>1338</v>
       </c>
       <c r="I255" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="256" spans="1:9">
@@ -12209,7 +12203,7 @@
         <v>1339</v>
       </c>
       <c r="I256" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="257" spans="1:9">
@@ -12238,7 +12232,7 @@
         <v>1340</v>
       </c>
       <c r="I257" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="258" spans="1:9">
@@ -12267,7 +12261,7 @@
         <v>1341</v>
       </c>
       <c r="I258" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="259" spans="1:9">
@@ -12296,7 +12290,7 @@
         <v>1342</v>
       </c>
       <c r="I259" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="260" spans="1:9">
@@ -12325,7 +12319,7 @@
         <v>1343</v>
       </c>
       <c r="I260" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="261" spans="1:9">
@@ -12354,7 +12348,7 @@
         <v>1344</v>
       </c>
       <c r="I261" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="262" spans="1:9">
@@ -12383,7 +12377,7 @@
         <v>1345</v>
       </c>
       <c r="I262" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="263" spans="1:9">
@@ -12412,7 +12406,7 @@
         <v>1346</v>
       </c>
       <c r="I263" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="264" spans="1:9">
@@ -12441,7 +12435,7 @@
         <v>1347</v>
       </c>
       <c r="I264" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="265" spans="1:9">
@@ -12470,7 +12464,7 @@
         <v>1348</v>
       </c>
       <c r="I265" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="266" spans="1:9">
@@ -12499,7 +12493,7 @@
         <v>1349</v>
       </c>
       <c r="I266" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="267" spans="1:9">
@@ -12528,7 +12522,7 @@
         <v>1350</v>
       </c>
       <c r="I267" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="268" spans="1:9">
@@ -12557,7 +12551,7 @@
         <v>1351</v>
       </c>
       <c r="I268" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="269" spans="1:9">
@@ -12586,7 +12580,7 @@
         <v>1352</v>
       </c>
       <c r="I269" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="270" spans="1:9">
@@ -12615,7 +12609,7 @@
         <v>1353</v>
       </c>
       <c r="I270" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="271" spans="1:9">
@@ -12644,7 +12638,7 @@
         <v>1354</v>
       </c>
       <c r="I271" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="272" spans="1:9">
@@ -12673,7 +12667,7 @@
         <v>1355</v>
       </c>
       <c r="I272" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="273" spans="1:9">
@@ -12702,7 +12696,7 @@
         <v>1356</v>
       </c>
       <c r="I273" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="274" spans="1:9">
@@ -12731,7 +12725,7 @@
         <v>1357</v>
       </c>
       <c r="I274" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="275" spans="1:9">
@@ -12760,7 +12754,7 @@
         <v>1358</v>
       </c>
       <c r="I275" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="276" spans="1:9">
@@ -12789,7 +12783,7 @@
         <v>1359</v>
       </c>
       <c r="I276" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="277" spans="1:9">
@@ -12818,7 +12812,7 @@
         <v>1360</v>
       </c>
       <c r="I277" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="278" spans="1:9">
@@ -12847,7 +12841,7 @@
         <v>1361</v>
       </c>
       <c r="I278" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="279" spans="1:9">
@@ -12876,7 +12870,7 @@
         <v>1362</v>
       </c>
       <c r="I279" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="280" spans="1:9">
@@ -12905,7 +12899,7 @@
         <v>1363</v>
       </c>
       <c r="I280" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="281" spans="1:9">
@@ -12934,7 +12928,7 @@
         <v>1364</v>
       </c>
       <c r="I281" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="282" spans="1:9">
@@ -12963,7 +12957,7 @@
         <v>1365</v>
       </c>
       <c r="I282" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="283" spans="1:9">
@@ -12992,7 +12986,7 @@
         <v>1366</v>
       </c>
       <c r="I283" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="284" spans="1:9">
@@ -13021,7 +13015,7 @@
         <v>1367</v>
       </c>
       <c r="I284" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="285" spans="1:9">
@@ -13050,7 +13044,7 @@
         <v>1368</v>
       </c>
       <c r="I285" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="286" spans="1:9">
@@ -13079,7 +13073,7 @@
         <v>1369</v>
       </c>
       <c r="I286" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="287" spans="1:9">
@@ -13108,7 +13102,7 @@
         <v>1370</v>
       </c>
       <c r="I287" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="288" spans="1:9">
@@ -13137,7 +13131,7 @@
         <v>1371</v>
       </c>
       <c r="I288" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="289" spans="1:9">
@@ -13166,7 +13160,7 @@
         <v>1372</v>
       </c>
       <c r="I289" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="290" spans="1:9">
@@ -13195,7 +13189,7 @@
         <v>1373</v>
       </c>
       <c r="I290" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="291" spans="1:9">
@@ -13224,7 +13218,7 @@
         <v>1374</v>
       </c>
       <c r="I291" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="292" spans="1:9">
@@ -13253,7 +13247,7 @@
         <v>1375</v>
       </c>
       <c r="I292" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="293" spans="1:9">
@@ -13282,7 +13276,7 @@
         <v>1376</v>
       </c>
       <c r="I293" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="294" spans="1:9">
@@ -13311,7 +13305,7 @@
         <v>1377</v>
       </c>
       <c r="I294" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="295" spans="1:9">
@@ -13340,7 +13334,7 @@
         <v>1378</v>
       </c>
       <c r="I295" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="296" spans="1:9">
@@ -13369,7 +13363,7 @@
         <v>1379</v>
       </c>
       <c r="I296" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="297" spans="1:9">
@@ -13398,7 +13392,7 @@
         <v>1380</v>
       </c>
       <c r="I297" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="298" spans="1:9">
@@ -13427,7 +13421,7 @@
         <v>1381</v>
       </c>
       <c r="I298" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="299" spans="1:9">
@@ -13456,7 +13450,7 @@
         <v>1382</v>
       </c>
       <c r="I299" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="300" spans="1:9">
@@ -13485,7 +13479,7 @@
         <v>1383</v>
       </c>
       <c r="I300" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="301" spans="1:9">
@@ -13514,7 +13508,7 @@
         <v>1384</v>
       </c>
       <c r="I301" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="302" spans="1:9">
@@ -13543,7 +13537,7 @@
         <v>1385</v>
       </c>
       <c r="I302" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="303" spans="1:9">
@@ -13572,7 +13566,7 @@
         <v>1386</v>
       </c>
       <c r="I303" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="304" spans="1:9">
@@ -13601,7 +13595,7 @@
         <v>1387</v>
       </c>
       <c r="I304" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="305" spans="1:9">
@@ -13630,7 +13624,7 @@
         <v>1388</v>
       </c>
       <c r="I305" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="306" spans="1:9">
@@ -13659,7 +13653,7 @@
         <v>1389</v>
       </c>
       <c r="I306" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="307" spans="1:9">
@@ -13688,7 +13682,7 @@
         <v>1390</v>
       </c>
       <c r="I307" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="308" spans="1:9">
@@ -13717,7 +13711,7 @@
         <v>1391</v>
       </c>
       <c r="I308" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="309" spans="1:9">
@@ -13746,7 +13740,7 @@
         <v>1392</v>
       </c>
       <c r="I309" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="310" spans="1:9">
@@ -13775,7 +13769,7 @@
         <v>1393</v>
       </c>
       <c r="I310" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="311" spans="1:9">
@@ -13804,7 +13798,7 @@
         <v>1394</v>
       </c>
       <c r="I311" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="312" spans="1:9">
@@ -13833,7 +13827,7 @@
         <v>1395</v>
       </c>
       <c r="I312" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="313" spans="1:9">
@@ -13862,7 +13856,7 @@
         <v>1396</v>
       </c>
       <c r="I313" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="314" spans="1:9">
@@ -13891,7 +13885,7 @@
         <v>1397</v>
       </c>
       <c r="I314" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="315" spans="1:9">
@@ -13920,7 +13914,7 @@
         <v>1398</v>
       </c>
       <c r="I315" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="316" spans="1:9">
@@ -13949,7 +13943,7 @@
         <v>1399</v>
       </c>
       <c r="I316" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="317" spans="1:9">
@@ -13978,7 +13972,7 @@
         <v>1400</v>
       </c>
       <c r="I317" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="318" spans="1:9">
@@ -14007,7 +14001,7 @@
         <v>1401</v>
       </c>
       <c r="I318" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="319" spans="1:9">
@@ -14036,7 +14030,7 @@
         <v>1402</v>
       </c>
       <c r="I319" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="320" spans="1:9">
@@ -14065,7 +14059,7 @@
         <v>1403</v>
       </c>
       <c r="I320" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="321" spans="1:9">
@@ -14094,7 +14088,7 @@
         <v>1404</v>
       </c>
       <c r="I321" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="322" spans="1:9">
@@ -14123,7 +14117,7 @@
         <v>1405</v>
       </c>
       <c r="I322" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="323" spans="1:9">
@@ -14152,7 +14146,7 @@
         <v>1406</v>
       </c>
       <c r="I323" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="324" spans="1:9">
@@ -14181,7 +14175,7 @@
         <v>1407</v>
       </c>
       <c r="I324" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="325" spans="1:9">
@@ -14210,7 +14204,7 @@
         <v>1408</v>
       </c>
       <c r="I325" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="326" spans="1:9">
@@ -14239,7 +14233,7 @@
         <v>1409</v>
       </c>
       <c r="I326" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="327" spans="1:9">
@@ -14268,7 +14262,7 @@
         <v>1410</v>
       </c>
       <c r="I327" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="328" spans="1:9">
@@ -14297,7 +14291,7 @@
         <v>1411</v>
       </c>
       <c r="I328" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="329" spans="1:9">
@@ -14326,7 +14320,7 @@
         <v>1412</v>
       </c>
       <c r="I329" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="330" spans="1:9">
@@ -14355,7 +14349,7 @@
         <v>1413</v>
       </c>
       <c r="I330" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="331" spans="1:9">
@@ -14384,7 +14378,7 @@
         <v>1414</v>
       </c>
       <c r="I331" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="332" spans="1:9">
@@ -14413,7 +14407,7 @@
         <v>1415</v>
       </c>
       <c r="I332" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="333" spans="1:9">
@@ -14442,7 +14436,7 @@
         <v>1416</v>
       </c>
       <c r="I333" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="334" spans="1:9">
@@ -14468,10 +14462,10 @@
         <v>1041</v>
       </c>
       <c r="H334" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="I334" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="335" spans="1:9">
@@ -14497,10 +14491,10 @@
         <v>1042</v>
       </c>
       <c r="H335" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="I335" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="336" spans="1:9">
@@ -14526,10 +14520,10 @@
         <v>1042</v>
       </c>
       <c r="H336" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="I336" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="337" spans="1:9">
@@ -14555,10 +14549,10 @@
         <v>1043</v>
       </c>
       <c r="H337" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="I337" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="338" spans="1:9">
@@ -14584,10 +14578,10 @@
         <v>1043</v>
       </c>
       <c r="H338" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="I338" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="339" spans="1:9">
@@ -14613,10 +14607,10 @@
         <v>1043</v>
       </c>
       <c r="H339" t="s">
-        <v>1422</v>
+        <v>1104</v>
       </c>
       <c r="I339" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="340" spans="1:9">
@@ -14645,7 +14639,7 @@
         <v>1105</v>
       </c>
       <c r="I340" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="341" spans="1:9">
@@ -14671,10 +14665,10 @@
         <v>1044</v>
       </c>
       <c r="H341" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="I341" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="342" spans="1:9">
@@ -14700,10 +14694,10 @@
         <v>1045</v>
       </c>
       <c r="H342" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="I342" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="343" spans="1:9">
@@ -14729,10 +14723,10 @@
         <v>1046</v>
       </c>
       <c r="H343" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="I343" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="344" spans="1:9">
@@ -14758,10 +14752,10 @@
         <v>1046</v>
       </c>
       <c r="H344" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="I344" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="345" spans="1:9">
@@ -14787,10 +14781,10 @@
         <v>1047</v>
       </c>
       <c r="H345" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="I345" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="346" spans="1:9">
@@ -14816,10 +14810,10 @@
         <v>1048</v>
       </c>
       <c r="H346" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="I346" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="347" spans="1:9">
@@ -14845,10 +14839,10 @@
         <v>1049</v>
       </c>
       <c r="H347" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="I347" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="348" spans="1:9">
@@ -14874,10 +14868,10 @@
         <v>1050</v>
       </c>
       <c r="H348" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="I348" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="349" spans="1:9">
@@ -14903,10 +14897,10 @@
         <v>1051</v>
       </c>
       <c r="H349" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="I349" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="350" spans="1:9">
@@ -14932,10 +14926,10 @@
         <v>1052</v>
       </c>
       <c r="H350" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="I350" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="351" spans="1:9">
@@ -14961,10 +14955,10 @@
         <v>1052</v>
       </c>
       <c r="H351" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="I351" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="352" spans="1:9">
@@ -14990,10 +14984,10 @@
         <v>1049</v>
       </c>
       <c r="H352" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="I352" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="353" spans="1:9">
@@ -15019,10 +15013,10 @@
         <v>1053</v>
       </c>
       <c r="H353" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="I353" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="354" spans="1:9">
@@ -15048,10 +15042,10 @@
         <v>1054</v>
       </c>
       <c r="H354" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="I354" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="355" spans="1:9">
@@ -15077,10 +15071,10 @@
         <v>1054</v>
       </c>
       <c r="H355" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="I355" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="356" spans="1:9">
@@ -15106,10 +15100,10 @@
         <v>1054</v>
       </c>
       <c r="H356" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="I356" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="357" spans="1:9">
@@ -15135,10 +15129,10 @@
         <v>1054</v>
       </c>
       <c r="H357" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="I357" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="358" spans="1:9">
@@ -15164,10 +15158,10 @@
         <v>1054</v>
       </c>
       <c r="H358" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="I358" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="359" spans="1:9">
@@ -15193,10 +15187,10 @@
         <v>1054</v>
       </c>
       <c r="H359" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="I359" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="360" spans="1:9">
@@ -15222,10 +15216,10 @@
         <v>1054</v>
       </c>
       <c r="H360" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="I360" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="361" spans="1:9">
@@ -15251,10 +15245,10 @@
         <v>1054</v>
       </c>
       <c r="H361" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="I361" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="362" spans="1:9">
@@ -15280,10 +15274,10 @@
         <v>1055</v>
       </c>
       <c r="H362" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="I362" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="363" spans="1:9">
@@ -15309,10 +15303,10 @@
         <v>1056</v>
       </c>
       <c r="H363" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="I363" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="364" spans="1:9">
@@ -15338,10 +15332,10 @@
         <v>1057</v>
       </c>
       <c r="H364" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="I364" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="365" spans="1:9">
@@ -15367,10 +15361,10 @@
         <v>1058</v>
       </c>
       <c r="H365" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="I365" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="366" spans="1:9">
@@ -15396,10 +15390,10 @@
         <v>1059</v>
       </c>
       <c r="H366" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="I366" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="367" spans="1:9">
@@ -15425,10 +15419,10 @@
         <v>1060</v>
       </c>
       <c r="H367" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="I367" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="368" spans="1:9">
@@ -15454,10 +15448,10 @@
         <v>1061</v>
       </c>
       <c r="H368" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="I368" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="369" spans="1:9">
@@ -15483,10 +15477,10 @@
         <v>1062</v>
       </c>
       <c r="H369" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="I369" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="370" spans="1:9">
@@ -15512,10 +15506,10 @@
         <v>1063</v>
       </c>
       <c r="H370" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="I370" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="371" spans="1:9">
@@ -15541,10 +15535,10 @@
         <v>1064</v>
       </c>
       <c r="H371" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="I371" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="372" spans="1:9">
@@ -15570,10 +15564,10 @@
         <v>1065</v>
       </c>
       <c r="H372" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="I372" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="373" spans="1:9">
@@ -15599,10 +15593,10 @@
         <v>1066</v>
       </c>
       <c r="H373" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="I373" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="374" spans="1:9">
@@ -15628,10 +15622,10 @@
         <v>1067</v>
       </c>
       <c r="H374" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="I374" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="375" spans="1:9">
@@ -15657,10 +15651,10 @@
         <v>1068</v>
       </c>
       <c r="H375" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="I375" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="376" spans="1:9">
@@ -15686,10 +15680,10 @@
         <v>1069</v>
       </c>
       <c r="H376" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="I376" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="377" spans="1:9">
@@ -15715,10 +15709,10 @@
         <v>1070</v>
       </c>
       <c r="H377" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="I377" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="378" spans="1:9">
@@ -15744,10 +15738,10 @@
         <v>1071</v>
       </c>
       <c r="H378" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="I378" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="379" spans="1:9">
@@ -15773,10 +15767,10 @@
         <v>1072</v>
       </c>
       <c r="H379" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="I379" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="380" spans="1:9">
@@ -15802,10 +15796,10 @@
         <v>830</v>
       </c>
       <c r="H380" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="I380" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="381" spans="1:9">
@@ -15831,10 +15825,10 @@
         <v>831</v>
       </c>
       <c r="H381" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="I381" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="382" spans="1:9">
@@ -15860,10 +15854,10 @@
         <v>1073</v>
       </c>
       <c r="H382" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="I382" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="383" spans="1:9">
@@ -15889,10 +15883,10 @@
         <v>833</v>
       </c>
       <c r="H383" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="I383" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="384" spans="1:9">
@@ -15918,10 +15912,10 @@
         <v>1074</v>
       </c>
       <c r="H384" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="I384" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="385" spans="1:9">
@@ -15947,10 +15941,10 @@
         <v>1075</v>
       </c>
       <c r="H385" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="I385" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="386" spans="1:9">
@@ -15976,10 +15970,10 @@
         <v>1075</v>
       </c>
       <c r="H386" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="I386" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="387" spans="1:9">
@@ -16005,10 +15999,10 @@
         <v>1076</v>
       </c>
       <c r="H387" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="I387" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="388" spans="1:9">
@@ -16034,10 +16028,10 @@
         <v>1077</v>
       </c>
       <c r="H388" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="I388" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="389" spans="1:9">
@@ -16063,10 +16057,10 @@
         <v>1078</v>
       </c>
       <c r="H389" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="I389" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="390" spans="1:9">
@@ -16092,10 +16086,10 @@
         <v>1079</v>
       </c>
       <c r="H390" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="I390" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="391" spans="1:9">
@@ -16121,10 +16115,10 @@
         <v>1080</v>
       </c>
       <c r="H391" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="I391" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="392" spans="1:9">
@@ -16150,10 +16144,10 @@
         <v>1081</v>
       </c>
       <c r="H392" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="I392" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="393" spans="1:9">
@@ -16179,10 +16173,10 @@
         <v>1082</v>
       </c>
       <c r="H393" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="I393" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="394" spans="1:9">
@@ -16208,10 +16202,10 @@
         <v>1083</v>
       </c>
       <c r="H394" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="I394" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="395" spans="1:9">
@@ -16237,10 +16231,10 @@
         <v>1084</v>
       </c>
       <c r="H395" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="I395" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="396" spans="1:9">
@@ -16266,10 +16260,10 @@
         <v>1085</v>
       </c>
       <c r="H396" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="I396" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
   </sheetData>
